--- a/results2/01_pollution_assessment/tables/site_scores.xlsx
+++ b/results2/01_pollution_assessment/tables/site_scores.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7091247669143035</v>
+        <v>0.7091247669143037</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1677375077220007</v>
+        <v>0.1677375077220012</v>
       </c>
       <c r="D2" t="n">
-        <v>0.798965591887121</v>
+        <v>0.7989655918871196</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4427709472438289</v>
+        <v>0.4427709472438209</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7855558975228261</v>
+        <v>0.7855558975228021</v>
       </c>
     </row>
     <row r="3">
@@ -495,13 +495,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2167585638314591</v>
+        <v>0.2167585638314606</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6047803541367353</v>
+        <v>0.6047803541367318</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7442456668686983</v>
+        <v>0.744245666868667</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +511,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6286746939651752</v>
+        <v>0.6286746939651751</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06647156120975564</v>
+        <v>0.06647156120975643</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6656764665207354</v>
+        <v>0.6656764665207331</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3387604629886576</v>
+        <v>0.3387604629886491</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7658443474909604</v>
+        <v>0.7658443474909403</v>
       </c>
     </row>
     <row r="5">
@@ -533,19 +533,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8800932714661193</v>
+        <v>0.8800932714661196</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3195168879916564</v>
+        <v>0.3195168879916555</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6652606656032427</v>
+        <v>0.6652606656032378</v>
       </c>
       <c r="F5" t="n">
-        <v>0.770258468850554</v>
+        <v>0.7702584688505384</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6468786075055876</v>
+        <v>0.6468786075055878</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05323944669522971</v>
+        <v>0.0532394466952302</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7904511107264416</v>
+        <v>0.7904511107264398</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4251875669364988</v>
+        <v>0.4251875669364883</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7605323636072933</v>
+        <v>0.7605323636072657</v>
       </c>
     </row>
     <row r="7">
@@ -577,19 +577,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7279918233250613</v>
+        <v>0.727991823325061</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3585344495010176</v>
+        <v>0.3585344495010188</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5943037918237695</v>
+        <v>0.5943037918237654</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1688852685552201</v>
+        <v>0.1688852685552136</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8062191432484073</v>
+        <v>0.8062191432483931</v>
       </c>
     </row>
     <row r="8">
@@ -605,13 +605,13 @@
         <v>0.1243343708121663</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3722821326479741</v>
+        <v>0.3722821326479753</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6978670173955738</v>
+        <v>0.6978670173955716</v>
       </c>
       <c r="F8" t="n">
-        <v>0.757750835312863</v>
+        <v>0.75775083531284</v>
       </c>
     </row>
     <row r="9">
@@ -624,16 +624,16 @@
         <v>0.7305560664097288</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2628372632935816</v>
+        <v>0.2628372632935821</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1488380274799418</v>
+        <v>0.1488380274799427</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5333636050614065</v>
+        <v>0.5333636050614057</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7565880033508275</v>
+        <v>0.7565880033508069</v>
       </c>
     </row>
     <row r="10">
@@ -643,19 +643,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.703626293380575</v>
+        <v>0.7036262933805751</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1569917990896843</v>
+        <v>0.1569917990896849</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6922043762413074</v>
+        <v>0.6922043762413057</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3650072834111876</v>
+        <v>0.3650072834111798</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7480972031591172</v>
+        <v>0.7480972031590953</v>
       </c>
     </row>
     <row r="11">
@@ -668,16 +668,16 @@
         <v>0.7347164995456573</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2313662052532729</v>
+        <v>0.2313662052532733</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7392217801227652</v>
+        <v>0.7392217801227631</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3797923728291189</v>
+        <v>0.3797923728291118</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7501913836513875</v>
+        <v>0.7501913836513673</v>
       </c>
     </row>
     <row r="12">
@@ -690,16 +690,16 @@
         <v>0.7369835324139299</v>
       </c>
       <c r="C12" t="n">
-        <v>0.356982961531185</v>
+        <v>0.3569829615311857</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6843856993255694</v>
+        <v>0.684385699325567</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3267093682018314</v>
+        <v>0.3267093682018247</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7509428048158128</v>
+        <v>0.7509428048157922</v>
       </c>
     </row>
     <row r="13">
@@ -709,19 +709,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8262459841917266</v>
+        <v>0.8262459841917267</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8353763655540833</v>
+        <v>0.8353763655540832</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4042713783357285</v>
+        <v>0.4042713783357294</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4400476949620589</v>
+        <v>0.4400476949620565</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6489124278824072</v>
+        <v>0.6489124278823726</v>
       </c>
     </row>
     <row r="14">
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6077509808753808</v>
+        <v>0.6077509808753807</v>
       </c>
       <c r="C14" t="n">
-        <v>0.06835576203787495</v>
+        <v>0.06835576203787568</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6153105197506307</v>
+        <v>0.6153105197506284</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2922973581114075</v>
+        <v>0.292297358111398</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7487909382913096</v>
+        <v>0.7487909382912835</v>
       </c>
     </row>
     <row r="15">
@@ -753,19 +753,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7690852153314278</v>
+        <v>0.7690852153314279</v>
       </c>
       <c r="C15" t="n">
-        <v>0.249700870956278</v>
+        <v>0.2497008709562782</v>
       </c>
       <c r="D15" t="n">
-        <v>0.775801237924713</v>
+        <v>0.775801237924711</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4278827233586254</v>
+        <v>0.4278827233586176</v>
       </c>
       <c r="F15" t="n">
-        <v>0.751575531370923</v>
+        <v>0.7515755313709036</v>
       </c>
     </row>
     <row r="16">
@@ -775,19 +775,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8386826106996476</v>
+        <v>0.8386826106996478</v>
       </c>
       <c r="C16" t="n">
-        <v>0.04709257085672156</v>
+        <v>0.0470925708567202</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5376222463619894</v>
+        <v>0.5376222463619922</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7301761449948144</v>
+        <v>0.7301761449947901</v>
       </c>
     </row>
     <row r="17">
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7802779271074589</v>
+        <v>0.7802779271074592</v>
       </c>
       <c r="C17" t="n">
-        <v>0.255827212485684</v>
+        <v>0.2558272124856837</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3325150760762266</v>
+        <v>0.3325150760762287</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6985766203434008</v>
+        <v>0.6985766203434007</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7503852932157062</v>
+        <v>0.750385293215687</v>
       </c>
     </row>
     <row r="18">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5876858241994664</v>
+        <v>0.5876858241994665</v>
       </c>
       <c r="C18" t="n">
-        <v>0.04530683441448455</v>
+        <v>0.04530683441448536</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6944808701403764</v>
+        <v>0.694480870140375</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3455520853906136</v>
+        <v>0.3455520853906031</v>
       </c>
       <c r="F18" t="n">
-        <v>0.759876756402703</v>
+        <v>0.7598767564026728</v>
       </c>
     </row>
     <row r="19">
@@ -841,19 +841,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7964659081029211</v>
+        <v>0.7964659081029213</v>
       </c>
       <c r="C19" t="n">
-        <v>0.08584501016750347</v>
+        <v>0.08584501016750272</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8481571580919156</v>
+        <v>0.8481571580919164</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7804245447806248</v>
+        <v>0.7804245447806194</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7623200057462031</v>
+        <v>0.7623200057461802</v>
       </c>
     </row>
     <row r="20">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6362549809300864</v>
+        <v>0.6362549809300865</v>
       </c>
       <c r="C20" t="n">
-        <v>0.07485262867027363</v>
+        <v>0.07485262867027449</v>
       </c>
       <c r="D20" t="n">
-        <v>0.653612303591281</v>
+        <v>0.653612303591279</v>
       </c>
       <c r="E20" t="n">
-        <v>0.325299830745804</v>
+        <v>0.3252998307457954</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7601353598482901</v>
+        <v>0.7601353598482663</v>
       </c>
     </row>
     <row r="21">
@@ -885,19 +885,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8003482237012152</v>
+        <v>0.8003482237012154</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2419013679921981</v>
+        <v>0.2419013679921975</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3484833053667775</v>
+        <v>0.3484833053667796</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7891951932507357</v>
+        <v>0.7891951932507351</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7490524473528627</v>
+        <v>0.7490524473528433</v>
       </c>
     </row>
     <row r="22">
@@ -907,19 +907,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8063898953783317</v>
+        <v>0.8063898953783319</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2780467618599704</v>
+        <v>0.2780467618599701</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3604905590444425</v>
+        <v>0.3604905590444441</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6807518972372334</v>
+        <v>0.6807518972372327</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7387270538508058</v>
+        <v>0.7387270538507834</v>
       </c>
     </row>
     <row r="23">
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7422413397005452</v>
+        <v>0.7422413397005454</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05157350544297486</v>
+        <v>0.05157350544297432</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3629411933565136</v>
+        <v>0.3629411933565158</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8030513428819215</v>
+        <v>0.80305134288192</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7455101947268287</v>
+        <v>0.7455101947268038</v>
       </c>
     </row>
     <row r="24">
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7232252740837974</v>
+        <v>0.7232252740837976</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1360352327353803</v>
+        <v>0.1360352327353806</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8136715931383036</v>
+        <v>0.8136715931383026</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4848512994420261</v>
+        <v>0.4848512994420174</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7741411761850231</v>
+        <v>0.7741411761849998</v>
       </c>
     </row>
     <row r="25">
@@ -973,19 +973,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8193148841952409</v>
+        <v>0.8193148841952411</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6210421965330576</v>
+        <v>0.6210421965330573</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3075256152230044</v>
+        <v>0.3075256152230059</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5748718643403246</v>
+        <v>0.5748718643403239</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7025633060144412</v>
+        <v>0.70256330601441</v>
       </c>
     </row>
     <row r="26">
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7666264230807084</v>
+        <v>0.7666264230807085</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5778541907334884</v>
+        <v>0.5778541907334892</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3205560971546626</v>
+        <v>0.3205560971546627</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7337012879203035</v>
+        <v>0.7337012879202774</v>
       </c>
     </row>
     <row r="27">
@@ -1017,19 +1017,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7877772225448479</v>
+        <v>0.7877772225448481</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7336505324974456</v>
+        <v>0.7336505324974463</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6184729918174637</v>
+        <v>0.6184729918174613</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1824228541802307</v>
+        <v>0.1824228541802248</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8128647082288755</v>
+        <v>0.8128647082288556</v>
       </c>
     </row>
     <row r="28">
@@ -1039,19 +1039,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7518137085893326</v>
+        <v>0.7518137085893327</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3265278207391524</v>
+        <v>0.3265278207391523</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2509512230282567</v>
+        <v>0.2509512230282577</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5675094424687919</v>
+        <v>0.56750944246879</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7364008248067845</v>
+        <v>0.7364008248067584</v>
       </c>
     </row>
     <row r="29">
@@ -1061,19 +1061,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8337423105573499</v>
+        <v>0.8337423105573502</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7404743776423659</v>
+        <v>0.7404743776423661</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2775865271557648</v>
+        <v>0.2775865271557654</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4464087665495666</v>
+        <v>0.4464087665495642</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6731857214960251</v>
+        <v>0.6731857214959892</v>
       </c>
     </row>
     <row r="30">
@@ -1083,19 +1083,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7022436991368406</v>
+        <v>0.7022436991368408</v>
       </c>
       <c r="C30" t="n">
-        <v>0.2653717981752134</v>
+        <v>0.2653717981752133</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2673803567664139</v>
+        <v>0.2673803567664153</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5488379680511039</v>
+        <v>0.5488379680511003</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7497493268172677</v>
+        <v>0.7497493268172331</v>
       </c>
     </row>
     <row r="31">
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7615377044604902</v>
+        <v>0.7615377044604905</v>
       </c>
       <c r="C31" t="n">
-        <v>0.04875783682812045</v>
+        <v>0.04875783682811954</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4373477187627963</v>
+        <v>0.4373477187627988</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8384142524647755</v>
+        <v>0.8384142524647726</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7366474216492691</v>
+        <v>0.7366474216492405</v>
       </c>
     </row>
     <row r="32">
@@ -1127,19 +1127,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8459751824921018</v>
+        <v>0.8459751824921024</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2539763829850383</v>
+        <v>0.2539763829850371</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5553311856587433</v>
+        <v>0.5553311856587462</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9046733436568524</v>
+        <v>0.9046733436568521</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7481435559277709</v>
+        <v>0.7481435559277521</v>
       </c>
     </row>
     <row r="33">
@@ -1149,19 +1149,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7650777061465834</v>
+        <v>0.7650777061465837</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4647974594516064</v>
+        <v>0.4647974594516068</v>
       </c>
       <c r="D33" t="n">
-        <v>0.148389957441748</v>
+        <v>0.148389957441749</v>
       </c>
       <c r="E33" t="n">
-        <v>0.510835503143886</v>
+        <v>0.5108355031438864</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7850860196548169</v>
+        <v>0.7850860196547934</v>
       </c>
     </row>
     <row r="34">
@@ -1171,19 +1171,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8247709471172159</v>
+        <v>0.824770947117216</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1689249056311732</v>
+        <v>0.1689249056311724</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3762340731923033</v>
+        <v>0.3762340731923051</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8360815133647423</v>
+        <v>0.836081513364742</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7476257355250789</v>
+        <v>0.7476257355250558</v>
       </c>
     </row>
     <row r="35">
@@ -1193,19 +1193,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7468283909914682</v>
+        <v>0.7468283909914681</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3049166420913133</v>
+        <v>0.3049166420913137</v>
       </c>
       <c r="D35" t="n">
-        <v>0.7302894633624724</v>
+        <v>0.73028946336247</v>
       </c>
       <c r="E35" t="n">
-        <v>0.361075297177478</v>
+        <v>0.3610752971774711</v>
       </c>
       <c r="F35" t="n">
-        <v>0.772156256293147</v>
+        <v>0.7721562562931285</v>
       </c>
     </row>
     <row r="36">
@@ -1218,16 +1218,16 @@
         <v>0.9303764793770116</v>
       </c>
       <c r="C36" t="n">
-        <v>0.458573875544025</v>
+        <v>0.4585738755440241</v>
       </c>
       <c r="D36" t="n">
-        <v>0.260302470813618</v>
+        <v>0.2603024708136203</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7724541677636293</v>
+        <v>0.7724541677636342</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7720536162389556</v>
+        <v>0.7720536162389428</v>
       </c>
     </row>
     <row r="37">
@@ -1237,19 +1237,19 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7852115085126452</v>
+        <v>0.7852115085126455</v>
       </c>
       <c r="C37" t="n">
         <v>0.2321473466852682</v>
       </c>
       <c r="D37" t="n">
-        <v>0.6968484911902292</v>
+        <v>0.6968484911902287</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5183921630181266</v>
+        <v>0.5183921630181216</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7992818896043902</v>
+        <v>0.7992818896043702</v>
       </c>
     </row>
     <row r="38">
@@ -1262,16 +1262,16 @@
         <v>0.6809510645077997</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2996609174777249</v>
+        <v>0.2996609174777254</v>
       </c>
       <c r="D38" t="n">
-        <v>0.7492012158787434</v>
+        <v>0.7492012158787402</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2831417466456803</v>
+        <v>0.28314174664567</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7937252578732176</v>
+        <v>0.7937252578731903</v>
       </c>
     </row>
     <row r="39">
@@ -1281,19 +1281,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8460379543807857</v>
+        <v>0.8460379543807858</v>
       </c>
       <c r="C39" t="n">
-        <v>0.751631456600225</v>
+        <v>0.7516314566002245</v>
       </c>
       <c r="D39" t="n">
-        <v>0.3635273327330441</v>
+        <v>0.3635273327330431</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4643722790391511</v>
+        <v>0.464372279039148</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8288048140900676</v>
+        <v>0.8288048140900334</v>
       </c>
     </row>
     <row r="40">
@@ -1303,19 +1303,19 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.9953762579781475</v>
+        <v>0.9953762579781473</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7673532420805019</v>
+        <v>0.767353242080501</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3959796958568036</v>
+        <v>0.3959796958568056</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6861255774206789</v>
+        <v>0.686125577420682</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7648877995327797</v>
+        <v>0.7648877995327592</v>
       </c>
     </row>
     <row r="41">
@@ -1325,19 +1325,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.9841023212894514</v>
+        <v>0.9841023212894516</v>
       </c>
       <c r="C41" t="n">
-        <v>0.5600214810462359</v>
+        <v>0.5600214810462354</v>
       </c>
       <c r="D41" t="n">
         <v>0.3967768603811527</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5709972054240168</v>
+        <v>0.5709972054240176</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8144003474220344</v>
+        <v>0.8144003474220192</v>
       </c>
     </row>
     <row r="42">
@@ -1347,19 +1347,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7585810500900777</v>
+        <v>0.7585810500900781</v>
       </c>
       <c r="C42" t="n">
         <v>0.4667827727203251</v>
       </c>
       <c r="D42" t="n">
-        <v>0.7759784767111337</v>
+        <v>0.7759784767111346</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4702391425525235</v>
+        <v>0.4702391425525194</v>
       </c>
       <c r="F42" t="n">
-        <v>0.8254563678348011</v>
+        <v>0.8254563678347897</v>
       </c>
     </row>
     <row r="43">
@@ -1369,19 +1369,19 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7956693735149968</v>
+        <v>0.7956693735149969</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1810095213816873</v>
+        <v>0.1810095213816865</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3912417159039634</v>
+        <v>0.3912417159039656</v>
       </c>
       <c r="E43" t="n">
-        <v>0.8239486625469222</v>
+        <v>0.8239486625469209</v>
       </c>
       <c r="F43" t="n">
-        <v>0.747010431340299</v>
+        <v>0.747010431340273</v>
       </c>
     </row>
     <row r="44">
@@ -1391,19 +1391,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6771623603094428</v>
+        <v>0.6771623603094429</v>
       </c>
       <c r="C44" t="n">
         <v>0.1119083621005343</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2897491905832655</v>
+        <v>0.2897491905832669</v>
       </c>
       <c r="E44" t="n">
-        <v>0.6590068344969838</v>
+        <v>0.6590068344969811</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7764373185568388</v>
+        <v>0.7764373185568146</v>
       </c>
     </row>
     <row r="45">
@@ -1413,19 +1413,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8374609964275739</v>
+        <v>0.8374609964275743</v>
       </c>
       <c r="C45" t="n">
-        <v>0.307651274043472</v>
+        <v>0.3076512740434716</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9246701795618307</v>
+        <v>0.92467017956183</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5716661094004387</v>
+        <v>0.5716661094004326</v>
       </c>
       <c r="F45" t="n">
-        <v>0.7821945094129127</v>
+        <v>0.7821945094128966</v>
       </c>
     </row>
     <row r="46">
@@ -1435,19 +1435,19 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6901909606210054</v>
+        <v>0.6901909606210055</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2311441212308845</v>
+        <v>0.2311441212308842</v>
       </c>
       <c r="D46" t="n">
-        <v>0.2377380361202379</v>
+        <v>0.2377380361202387</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5703740369574766</v>
+        <v>0.5703740369574734</v>
       </c>
       <c r="F46" t="n">
-        <v>0.7616996987008138</v>
+        <v>0.7616996987007841</v>
       </c>
     </row>
     <row r="47">
@@ -1457,19 +1457,19 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8474928591104063</v>
+        <v>0.8474928591104065</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1905669732440751</v>
+        <v>0.1905669732440738</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4002449079750925</v>
+        <v>0.4002449079750937</v>
       </c>
       <c r="E47" t="n">
-        <v>0.8517981278243015</v>
+        <v>0.8517981278243016</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7118773530610787</v>
+        <v>0.7118773530610593</v>
       </c>
     </row>
     <row r="48">
@@ -1479,19 +1479,19 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8770755274381332</v>
+        <v>0.877075527438133</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2382591770849164</v>
+        <v>0.2382591770849151</v>
       </c>
       <c r="D48" t="n">
-        <v>0.5068305286480597</v>
+        <v>0.5068305286480598</v>
       </c>
       <c r="E48" t="n">
-        <v>0.8367187553628429</v>
+        <v>0.8367187553628426</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7169463056239579</v>
+        <v>0.7169463056239358</v>
       </c>
     </row>
     <row r="49">
@@ -1504,16 +1504,16 @@
         <v>0.8451043324207419</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2019546675842257</v>
+        <v>0.2019546675842244</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3594653111268247</v>
+        <v>0.3594653111268261</v>
       </c>
       <c r="E49" t="n">
-        <v>0.8815655326223684</v>
+        <v>0.8815655326223694</v>
       </c>
       <c r="F49" t="n">
-        <v>0.7167186346657101</v>
+        <v>0.7167186346656916</v>
       </c>
     </row>
     <row r="50">
@@ -1523,19 +1523,19 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8762346805878933</v>
+        <v>0.8762346805878934</v>
       </c>
       <c r="C50" t="n">
-        <v>0.3630942142742877</v>
+        <v>0.3630942142742867</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3119405788244728</v>
+        <v>0.311940578824476</v>
       </c>
       <c r="E50" t="n">
-        <v>0.8277979554211037</v>
+        <v>0.8277979554211068</v>
       </c>
       <c r="F50" t="n">
-        <v>0.7568288347631293</v>
+        <v>0.7568288347631141</v>
       </c>
     </row>
     <row r="51">
@@ -1548,16 +1548,16 @@
         <v>0.7588478232157417</v>
       </c>
       <c r="C51" t="n">
-        <v>0.3167119527594969</v>
+        <v>0.3167119527594968</v>
       </c>
       <c r="D51" t="n">
-        <v>0.2209422543969482</v>
+        <v>0.2209422543969492</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5766933317180701</v>
+        <v>0.5766933317180695</v>
       </c>
       <c r="F51" t="n">
-        <v>0.7500130635854799</v>
+        <v>0.7500130635854579</v>
       </c>
     </row>
     <row r="52">
@@ -1567,19 +1567,19 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.9136231863318726</v>
+        <v>0.9136231863318731</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3993084808245853</v>
+        <v>0.3993084808245841</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3711008038204382</v>
+        <v>0.3711008038204412</v>
       </c>
       <c r="E52" t="n">
-        <v>0.8632985768585759</v>
+        <v>0.8632985768585799</v>
       </c>
       <c r="F52" t="n">
-        <v>0.7282621040825605</v>
+        <v>0.7282621040825404</v>
       </c>
     </row>
     <row r="53">
@@ -1592,16 +1592,16 @@
         <v>0.8764051283441353</v>
       </c>
       <c r="C53" t="n">
-        <v>0.3732607106106511</v>
+        <v>0.37326071061065</v>
       </c>
       <c r="D53" t="n">
-        <v>0.2797029759557901</v>
+        <v>0.2797029759557931</v>
       </c>
       <c r="E53" t="n">
-        <v>0.847912227239337</v>
+        <v>0.84791222723934</v>
       </c>
       <c r="F53" t="n">
-        <v>0.7606666040799179</v>
+        <v>0.7606666040799034</v>
       </c>
     </row>
     <row r="54">
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6840831390914569</v>
+        <v>0.684083139091457</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1501189825475215</v>
+        <v>0.1501189825475213</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3130535724824427</v>
+        <v>0.3130535724824433</v>
       </c>
       <c r="E54" t="n">
-        <v>0.5784588062600634</v>
+        <v>0.5784588062600596</v>
       </c>
       <c r="F54" t="n">
-        <v>0.792160301483561</v>
+        <v>0.7921603014835371</v>
       </c>
     </row>
     <row r="55">
@@ -1633,19 +1633,19 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7882307925579742</v>
+        <v>0.7882307925579745</v>
       </c>
       <c r="C55" t="n">
         <v>0.3193390226271521</v>
       </c>
       <c r="D55" t="n">
-        <v>0.3269843265820655</v>
+        <v>0.3269843265820673</v>
       </c>
       <c r="E55" t="n">
-        <v>0.6916024661860833</v>
+        <v>0.6916024661860847</v>
       </c>
       <c r="F55" t="n">
-        <v>0.7581856703901667</v>
+        <v>0.7581856703901511</v>
       </c>
     </row>
     <row r="56">
@@ -1658,16 +1658,16 @@
         <v>0.6703269276465558</v>
       </c>
       <c r="C56" t="n">
-        <v>0.2596138697236148</v>
+        <v>0.2596138697236153</v>
       </c>
       <c r="D56" t="n">
-        <v>0.1645525877306225</v>
+        <v>0.1645525877306223</v>
       </c>
       <c r="E56" t="n">
-        <v>0.4148917956290014</v>
+        <v>0.4148917956289985</v>
       </c>
       <c r="F56" t="n">
-        <v>0.7701744679244497</v>
+        <v>0.7701744679244268</v>
       </c>
     </row>
     <row r="57">
@@ -1677,19 +1677,19 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.9392330210254026</v>
+        <v>0.9392330210254027</v>
       </c>
       <c r="C57" t="n">
-        <v>0.4385150888754037</v>
+        <v>0.4385150888754025</v>
       </c>
       <c r="D57" t="n">
-        <v>0.4412635478076419</v>
+        <v>0.4412635478076444</v>
       </c>
       <c r="E57" t="n">
-        <v>0.822463306487677</v>
+        <v>0.8224633064876804</v>
       </c>
       <c r="F57" t="n">
-        <v>0.7543488977824228</v>
+        <v>0.7543488977824084</v>
       </c>
     </row>
     <row r="58">
@@ -1699,13 +1699,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6604995537392525</v>
+        <v>0.6604995537392527</v>
       </c>
       <c r="C58" t="n">
-        <v>0.5686787689188048</v>
+        <v>0.5686787689188095</v>
       </c>
       <c r="D58" t="n">
-        <v>0.2754157834418672</v>
+        <v>0.2754157834418721</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -1724,16 +1724,16 @@
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8037470370222717</v>
+        <v>0.8037470370222708</v>
       </c>
       <c r="D59" t="n">
-        <v>0.3800351334364745</v>
+        <v>0.3800351334364754</v>
       </c>
       <c r="E59" t="n">
-        <v>0.6688487987714752</v>
+        <v>0.6688487987714776</v>
       </c>
       <c r="F59" t="n">
-        <v>0.7704369666940978</v>
+        <v>0.7704369666940747</v>
       </c>
     </row>
     <row r="60">
@@ -1743,19 +1743,19 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7515132554164451</v>
+        <v>0.751513255416445</v>
       </c>
       <c r="C60" t="n">
-        <v>0.4551597124388143</v>
+        <v>0.4551597124388147</v>
       </c>
       <c r="D60" t="n">
-        <v>0.2015946899947423</v>
+        <v>0.2015946899947421</v>
       </c>
       <c r="E60" t="n">
-        <v>0.4363620681431859</v>
+        <v>0.4363620681431836</v>
       </c>
       <c r="F60" t="n">
-        <v>0.7225329117847107</v>
+        <v>0.7225329117846823</v>
       </c>
     </row>
     <row r="61">
@@ -1765,19 +1765,19 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.830311344859837</v>
+        <v>0.8303113448598373</v>
       </c>
       <c r="C61" t="n">
-        <v>0.3891229843187466</v>
+        <v>0.3891229843187465</v>
       </c>
       <c r="D61" t="n">
-        <v>0.318489914827783</v>
+        <v>0.3184899148277838</v>
       </c>
       <c r="E61" t="n">
-        <v>0.6052835693787584</v>
+        <v>0.6052835693787575</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7376655860891976</v>
+        <v>0.7376655860891729</v>
       </c>
     </row>
     <row r="62">
@@ -1787,19 +1787,19 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.9119325933207973</v>
+        <v>0.9119325933207975</v>
       </c>
       <c r="C62" t="n">
-        <v>0.7603655293843273</v>
+        <v>0.7603655293843268</v>
       </c>
       <c r="D62" t="n">
-        <v>0.3043965978950069</v>
+        <v>0.3043965978950078</v>
       </c>
       <c r="E62" t="n">
-        <v>0.5785364790522117</v>
+        <v>0.5785364790522112</v>
       </c>
       <c r="F62" t="n">
-        <v>0.7716556961787105</v>
+        <v>0.7716556961786785</v>
       </c>
     </row>
     <row r="63">
@@ -1809,19 +1809,19 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7971204209280016</v>
+        <v>0.7971204209280017</v>
       </c>
       <c r="C63" t="n">
-        <v>0.5798140873269304</v>
+        <v>0.5798140873269296</v>
       </c>
       <c r="D63" t="n">
-        <v>0.4165534649756109</v>
+        <v>0.4165534649756118</v>
       </c>
       <c r="E63" t="n">
-        <v>0.6630882448045253</v>
+        <v>0.6630882448045227</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7220425538343375</v>
+        <v>0.7220425538342956</v>
       </c>
     </row>
     <row r="64">
@@ -1831,19 +1831,19 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.9122395616013799</v>
+        <v>0.9122395616013804</v>
       </c>
       <c r="C64" t="n">
-        <v>0.4359222724781974</v>
+        <v>0.4359222724781966</v>
       </c>
       <c r="D64" t="n">
-        <v>0.9305841480038568</v>
+        <v>0.9305841480038566</v>
       </c>
       <c r="E64" t="n">
-        <v>0.591156995313144</v>
+        <v>0.5911569953131404</v>
       </c>
       <c r="F64" t="n">
-        <v>0.7710129887196875</v>
+        <v>0.7710129887196723</v>
       </c>
     </row>
     <row r="65">
@@ -1853,19 +1853,19 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7652400454075401</v>
+        <v>0.7652400454075402</v>
       </c>
       <c r="C65" t="n">
-        <v>0.1356395778117912</v>
+        <v>0.1356395778117908</v>
       </c>
       <c r="D65" t="n">
-        <v>0.9265428841035159</v>
+        <v>0.9265428841035157</v>
       </c>
       <c r="E65" t="n">
-        <v>0.6484214003042286</v>
+        <v>0.6484214003042217</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7151134393055502</v>
+        <v>0.7151134393055265</v>
       </c>
     </row>
     <row r="66">
@@ -1875,19 +1875,19 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7391569573062401</v>
+        <v>0.7391569573062403</v>
       </c>
       <c r="C66" t="n">
-        <v>0.3072133175084963</v>
+        <v>0.3072133175084965</v>
       </c>
       <c r="D66" t="n">
-        <v>0.8155318199056019</v>
+        <v>0.8155318199056002</v>
       </c>
       <c r="E66" t="n">
-        <v>0.4207199344518459</v>
+        <v>0.4207199344518385</v>
       </c>
       <c r="F66" t="n">
-        <v>0.786678027198408</v>
+        <v>0.7866780271983842</v>
       </c>
     </row>
     <row r="67">
@@ -1897,19 +1897,19 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8940902313284183</v>
+        <v>0.8940902313284184</v>
       </c>
       <c r="C67" t="n">
-        <v>0.4247578902930314</v>
+        <v>0.424757890293031</v>
       </c>
       <c r="D67" t="n">
-        <v>0.8906618809242363</v>
+        <v>0.8906618809242353</v>
       </c>
       <c r="E67" t="n">
-        <v>0.54546408259546</v>
+        <v>0.5454640825954553</v>
       </c>
       <c r="F67" t="n">
-        <v>0.7824886270834316</v>
+        <v>0.7824886270834169</v>
       </c>
     </row>
     <row r="68">
@@ -1919,19 +1919,19 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8250779560582383</v>
+        <v>0.8250779560582384</v>
       </c>
       <c r="C68" t="n">
-        <v>0.4182706530637395</v>
+        <v>0.4182706530637396</v>
       </c>
       <c r="D68" t="n">
-        <v>0.7608516890629571</v>
+        <v>0.7608516890629556</v>
       </c>
       <c r="E68" t="n">
-        <v>0.4093919103211174</v>
+        <v>0.4093919103211121</v>
       </c>
       <c r="F68" t="n">
-        <v>0.7939436206534571</v>
+        <v>0.793943620653442</v>
       </c>
     </row>
     <row r="69">
@@ -1941,19 +1941,19 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8739687553869456</v>
+        <v>0.8739687553869459</v>
       </c>
       <c r="C69" t="n">
-        <v>0.6099989027682221</v>
+        <v>0.6099989027682228</v>
       </c>
       <c r="D69" t="n">
-        <v>0.6155795561112812</v>
+        <v>0.6155795561112787</v>
       </c>
       <c r="E69" t="n">
-        <v>0.2234275109062756</v>
+        <v>0.2234275109062729</v>
       </c>
       <c r="F69" t="n">
-        <v>0.877145737636462</v>
+        <v>0.8771457376364615</v>
       </c>
     </row>
     <row r="70">
@@ -1963,19 +1963,19 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.9835234046584395</v>
+        <v>0.9835234046584397</v>
       </c>
       <c r="C70" t="n">
-        <v>0.6006598001850408</v>
+        <v>0.6006598001850403</v>
       </c>
       <c r="D70" t="n">
-        <v>0.4358503558547491</v>
+        <v>0.4358503558547509</v>
       </c>
       <c r="E70" t="n">
-        <v>0.7315333046322507</v>
+        <v>0.7315333046322562</v>
       </c>
       <c r="F70" t="n">
-        <v>0.8745476791225579</v>
+        <v>0.8745476791225627</v>
       </c>
     </row>
     <row r="71">
@@ -1985,19 +1985,19 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.9184463115640762</v>
+        <v>0.9184463115640765</v>
       </c>
       <c r="C71" t="n">
-        <v>0.3693483039036854</v>
+        <v>0.3693483039036847</v>
       </c>
       <c r="D71" t="n">
-        <v>0.9917865112870107</v>
+        <v>0.99178651128701</v>
       </c>
       <c r="E71" t="n">
-        <v>0.6389593765636699</v>
+        <v>0.6389593765636672</v>
       </c>
       <c r="F71" t="n">
-        <v>0.7762766903664403</v>
+        <v>0.7762766903664269</v>
       </c>
     </row>
     <row r="72">
@@ -2007,19 +2007,19 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8294712462074414</v>
+        <v>0.8294712462074416</v>
       </c>
       <c r="C72" t="n">
-        <v>0.3173156729492452</v>
+        <v>0.317315672949245</v>
       </c>
       <c r="D72" t="n">
-        <v>0.8721628892442209</v>
+        <v>0.8721628892442201</v>
       </c>
       <c r="E72" t="n">
-        <v>0.5136670117031247</v>
+        <v>0.5136670117031181</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7893199397770992</v>
+        <v>0.789319939777078</v>
       </c>
     </row>
     <row r="73">
@@ -2029,19 +2029,19 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8274302307678301</v>
+        <v>0.8274302307678302</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1834626802705062</v>
+        <v>0.1834626802705054</v>
       </c>
       <c r="D73" t="n">
-        <v>0.9971534514210368</v>
+        <v>0.9971534514210357</v>
       </c>
       <c r="E73" t="n">
-        <v>0.6597045457676304</v>
+        <v>0.6597045457676233</v>
       </c>
       <c r="F73" t="n">
-        <v>0.7092499759293581</v>
+        <v>0.7092499759293359</v>
       </c>
     </row>
     <row r="74">
@@ -2051,19 +2051,19 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8003666223219799</v>
+        <v>0.8003666223219802</v>
       </c>
       <c r="C74" t="n">
-        <v>0.308312699889505</v>
+        <v>0.3083126998895053</v>
       </c>
       <c r="D74" t="n">
-        <v>0.7834227669018522</v>
+        <v>0.783422766901851</v>
       </c>
       <c r="E74" t="n">
-        <v>0.4482433003920447</v>
+        <v>0.448243300392039</v>
       </c>
       <c r="F74" t="n">
-        <v>0.7854731098512538</v>
+        <v>0.7854731098512393</v>
       </c>
     </row>
     <row r="75">
@@ -2073,19 +2073,19 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8469635828504277</v>
+        <v>0.8469635828504279</v>
       </c>
       <c r="C75" t="n">
-        <v>0.4063771845005376</v>
+        <v>0.4063771845005375</v>
       </c>
       <c r="D75" t="n">
-        <v>0.8197582676837079</v>
+        <v>0.8197582676837067</v>
       </c>
       <c r="E75" t="n">
-        <v>0.4674652737490987</v>
+        <v>0.467465273749093</v>
       </c>
       <c r="F75" t="n">
-        <v>0.7824868365599437</v>
+        <v>0.7824868365599271</v>
       </c>
     </row>
     <row r="76">
@@ -2095,19 +2095,19 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7148279978097888</v>
+        <v>0.714827997809789</v>
       </c>
       <c r="C76" t="n">
-        <v>0.1832737561121997</v>
+        <v>0.1832737561121998</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3210867225976975</v>
+        <v>0.3210867225976988</v>
       </c>
       <c r="E76" t="n">
-        <v>0.5948329624043313</v>
+        <v>0.5948329624043284</v>
       </c>
       <c r="F76" t="n">
-        <v>0.7885573700392169</v>
+        <v>0.7885573700391918</v>
       </c>
     </row>
     <row r="77">
@@ -2117,19 +2117,19 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7689125549160377</v>
+        <v>0.7689125549160379</v>
       </c>
       <c r="C77" t="n">
-        <v>0.3963011531214316</v>
+        <v>0.3963011531214323</v>
       </c>
       <c r="D77" t="n">
-        <v>0.7014490923917669</v>
+        <v>0.7014490923917638</v>
       </c>
       <c r="E77" t="n">
-        <v>0.2733417908781695</v>
+        <v>0.273341790878162</v>
       </c>
       <c r="F77" t="n">
-        <v>0.8149703048293772</v>
+        <v>0.8149703048293563</v>
       </c>
     </row>
     <row r="78">
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.8868367201860423</v>
+        <v>0.8868367201860424</v>
       </c>
       <c r="C78" t="n">
-        <v>0.3609009763570136</v>
+        <v>0.3609009763570128</v>
       </c>
       <c r="D78" t="n">
-        <v>0.9469359373120592</v>
+        <v>0.9469359373120586</v>
       </c>
       <c r="E78" t="n">
-        <v>0.5891226408574327</v>
+        <v>0.5891226408574283</v>
       </c>
       <c r="F78" t="n">
-        <v>0.7594178955002712</v>
+        <v>0.759417895500252</v>
       </c>
     </row>
     <row r="79">
@@ -2161,19 +2161,19 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.8233563135554917</v>
+        <v>0.8233563135554914</v>
       </c>
       <c r="C79" t="n">
-        <v>0.1120291839475738</v>
+        <v>0.1120291839475724</v>
       </c>
       <c r="D79" t="n">
-        <v>0.5793698075375678</v>
+        <v>0.5793698075375695</v>
       </c>
       <c r="E79" t="n">
-        <v>0.960199985700408</v>
+        <v>0.9601999857004078</v>
       </c>
       <c r="F79" t="n">
-        <v>0.6757104389857024</v>
+        <v>0.6757104389856811</v>
       </c>
     </row>
     <row r="80">
@@ -2186,16 +2186,16 @@
         <v>0.8285596213533652</v>
       </c>
       <c r="C80" t="n">
-        <v>0.238852489390855</v>
+        <v>0.2388524893908544</v>
       </c>
       <c r="D80" t="n">
-        <v>0.2962589920908447</v>
+        <v>0.2962589920908468</v>
       </c>
       <c r="E80" t="n">
-        <v>0.7392427340994394</v>
+        <v>0.7392427340994395</v>
       </c>
       <c r="F80" t="n">
-        <v>0.7518572819734516</v>
+        <v>0.7518572819734274</v>
       </c>
     </row>
     <row r="81">
@@ -2205,19 +2205,19 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.9140930531170128</v>
+        <v>0.9140930531170132</v>
       </c>
       <c r="C81" t="n">
-        <v>0.6026541988941602</v>
+        <v>0.6026541988941604</v>
       </c>
       <c r="D81" t="n">
-        <v>0.6917978909572019</v>
+        <v>0.6917978909571993</v>
       </c>
       <c r="E81" t="n">
-        <v>0.2902385430704083</v>
+        <v>0.2902385430704036</v>
       </c>
       <c r="F81" t="n">
-        <v>0.8048759779668196</v>
+        <v>0.8048759779668059</v>
       </c>
     </row>
     <row r="82">
@@ -2227,19 +2227,19 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.8606921650803605</v>
+        <v>0.8606921650803607</v>
       </c>
       <c r="C82" t="n">
         <v>0.4597804838904143</v>
       </c>
       <c r="D82" t="n">
-        <v>0.8013763283652944</v>
+        <v>0.8013763283652923</v>
       </c>
       <c r="E82" t="n">
-        <v>0.4042377287407671</v>
+        <v>0.4042377287407614</v>
       </c>
       <c r="F82" t="n">
-        <v>0.7897417482773753</v>
+        <v>0.789741748277356</v>
       </c>
     </row>
     <row r="83">
@@ -2249,19 +2249,19 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.9601956156287582</v>
+        <v>0.9601956156287584</v>
       </c>
       <c r="C83" t="n">
-        <v>0.6774245339073575</v>
+        <v>0.6774245339073574</v>
       </c>
       <c r="D83" t="n">
-        <v>0.8736895786411072</v>
+        <v>0.8736895786411059</v>
       </c>
       <c r="E83" t="n">
-        <v>0.4536038224766525</v>
+        <v>0.4536038224766482</v>
       </c>
       <c r="F83" t="n">
-        <v>0.7870286790142916</v>
+        <v>0.7870286790142742</v>
       </c>
     </row>
     <row r="84">
@@ -2271,19 +2271,19 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7380904703193053</v>
+        <v>0.7380904703193052</v>
       </c>
       <c r="C84" t="n">
-        <v>0.2912336694804586</v>
+        <v>0.2912336694804598</v>
       </c>
       <c r="D84" t="n">
-        <v>0.6375611948742576</v>
+        <v>0.6375611948742536</v>
       </c>
       <c r="E84" t="n">
-        <v>0.2666704067010693</v>
+        <v>0.2666704067010618</v>
       </c>
       <c r="F84" t="n">
-        <v>0.7504558580452693</v>
+        <v>0.7504558580452532</v>
       </c>
     </row>
     <row r="85">
@@ -2293,19 +2293,19 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7892724020788892</v>
+        <v>0.7892724020788893</v>
       </c>
       <c r="C85" t="n">
-        <v>0.4444399889591618</v>
+        <v>0.4444399889591628</v>
       </c>
       <c r="D85" t="n">
-        <v>0.6298951116061803</v>
+        <v>0.6298951116061778</v>
       </c>
       <c r="E85" t="n">
-        <v>0.2641449471900739</v>
+        <v>0.264144947190068</v>
       </c>
       <c r="F85" t="n">
-        <v>0.768786622382337</v>
+        <v>0.7687866223823187</v>
       </c>
     </row>
     <row r="86">
@@ -2315,19 +2315,19 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7233646733011444</v>
+        <v>0.7233646733011445</v>
       </c>
       <c r="C86" t="n">
-        <v>0.2313491887702025</v>
+        <v>0.2313491887702031</v>
       </c>
       <c r="D86" t="n">
-        <v>0.2804204711242173</v>
+        <v>0.2804204711242175</v>
       </c>
       <c r="E86" t="n">
-        <v>0.499804470291957</v>
+        <v>0.4998044702919543</v>
       </c>
       <c r="F86" t="n">
-        <v>0.8021977957362654</v>
+        <v>0.8021977957362479</v>
       </c>
     </row>
     <row r="87">
@@ -2337,19 +2337,19 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.875128736414263</v>
+        <v>0.8751287364142633</v>
       </c>
       <c r="C87" t="n">
-        <v>0.3685187801931973</v>
+        <v>0.3685187801931963</v>
       </c>
       <c r="D87" t="n">
-        <v>0.3891929832164914</v>
+        <v>0.389192983216494</v>
       </c>
       <c r="E87" t="n">
-        <v>0.8119762345927752</v>
+        <v>0.8119762345927778</v>
       </c>
       <c r="F87" t="n">
-        <v>0.7609708073913313</v>
+        <v>0.7609708073913152</v>
       </c>
     </row>
     <row r="88">
@@ -2359,19 +2359,19 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7848120715046778</v>
+        <v>0.784812071504678</v>
       </c>
       <c r="C88" t="n">
-        <v>0.1462777687395368</v>
+        <v>0.1462777687395365</v>
       </c>
       <c r="D88" t="n">
-        <v>0.8922259183183952</v>
+        <v>0.8922259183183946</v>
       </c>
       <c r="E88" t="n">
-        <v>0.5814298078907223</v>
+        <v>0.5814298078907149</v>
       </c>
       <c r="F88" t="n">
-        <v>0.7687614128057809</v>
+        <v>0.7687614128057583</v>
       </c>
     </row>
     <row r="89">
@@ -2384,16 +2384,16 @@
         <v>0.8962372036855233</v>
       </c>
       <c r="C89" t="n">
-        <v>0.4348098685387968</v>
+        <v>0.4348098685387959</v>
       </c>
       <c r="D89" t="n">
-        <v>0.3965914536180176</v>
+        <v>0.3965914536180198</v>
       </c>
       <c r="E89" t="n">
-        <v>0.7830731655905698</v>
+        <v>0.7830731655905721</v>
       </c>
       <c r="F89" t="n">
-        <v>0.7701284255064162</v>
+        <v>0.7701284255064026</v>
       </c>
     </row>
     <row r="90">
@@ -2406,16 +2406,16 @@
         <v>0.9243852342970097</v>
       </c>
       <c r="C90" t="n">
-        <v>0.4221497601220637</v>
+        <v>0.4221497601220626</v>
       </c>
       <c r="D90" t="n">
-        <v>0.4044050450246408</v>
+        <v>0.4044050450246443</v>
       </c>
       <c r="E90" t="n">
-        <v>0.932674398844717</v>
+        <v>0.9326743988447215</v>
       </c>
       <c r="F90" t="n">
-        <v>0.7785836966605392</v>
+        <v>0.7785836966605283</v>
       </c>
     </row>
     <row r="91">
@@ -2428,16 +2428,16 @@
         <v>0.6659525473959952</v>
       </c>
       <c r="C91" t="n">
-        <v>0.1907604360551644</v>
+        <v>0.1907604360551649</v>
       </c>
       <c r="D91" t="n">
-        <v>0.2120560188411656</v>
+        <v>0.2120560188411664</v>
       </c>
       <c r="E91" t="n">
-        <v>0.5112169072215824</v>
+        <v>0.5112169072215799</v>
       </c>
       <c r="F91" t="n">
-        <v>0.7704090844901753</v>
+        <v>0.770409084490152</v>
       </c>
     </row>
     <row r="92">
@@ -2447,19 +2447,19 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7859138369855304</v>
+        <v>0.7859138369855305</v>
       </c>
       <c r="C92" t="n">
-        <v>0.3169607776533303</v>
+        <v>0.3169607776533307</v>
       </c>
       <c r="D92" t="n">
-        <v>0.2575029104453112</v>
+        <v>0.2575029104453116</v>
       </c>
       <c r="E92" t="n">
-        <v>0.5388701473415956</v>
+        <v>0.5388701473415951</v>
       </c>
       <c r="F92" t="n">
-        <v>0.7618719257681374</v>
+        <v>0.7618719257681195</v>
       </c>
     </row>
     <row r="93">
@@ -2472,16 +2472,16 @@
         <v>0.7947099944313374</v>
       </c>
       <c r="C93" t="n">
-        <v>0.577999913709262</v>
+        <v>0.5779999137092608</v>
       </c>
       <c r="D93" t="n">
-        <v>0.3165795616844463</v>
+        <v>0.3165795616844468</v>
       </c>
       <c r="E93" t="n">
-        <v>0.6161411388304801</v>
+        <v>0.6161411388304789</v>
       </c>
       <c r="F93" t="n">
-        <v>0.7915512887384881</v>
+        <v>0.7915512887384596</v>
       </c>
     </row>
     <row r="94">
@@ -2491,19 +2491,19 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.8190274368796994</v>
+        <v>0.8190274368796995</v>
       </c>
       <c r="C94" t="n">
-        <v>0.6201165525232751</v>
+        <v>0.620116552523275</v>
       </c>
       <c r="D94" t="n">
-        <v>0.1974358680657205</v>
+        <v>0.19743586806572</v>
       </c>
       <c r="E94" t="n">
-        <v>0.4869455156618502</v>
+        <v>0.4869455156618487</v>
       </c>
       <c r="F94" t="n">
-        <v>0.7798435692424568</v>
+        <v>0.7798435692424254</v>
       </c>
     </row>
     <row r="95">
@@ -2516,16 +2516,16 @@
         <v>0.8436684796469525</v>
       </c>
       <c r="C95" t="n">
-        <v>0.4551970726735331</v>
+        <v>0.4551970726735337</v>
       </c>
       <c r="D95" t="n">
-        <v>0.1947885457111358</v>
+        <v>0.1947885457111368</v>
       </c>
       <c r="E95" t="n">
-        <v>0.5539703933454581</v>
+        <v>0.5539703933454589</v>
       </c>
       <c r="F95" t="n">
-        <v>0.7683254537680595</v>
+        <v>0.7683254537680424</v>
       </c>
     </row>
     <row r="96">
@@ -2535,19 +2535,19 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.7577297875553425</v>
+        <v>0.7577297875553426</v>
       </c>
       <c r="C96" t="n">
-        <v>0.5137274405689022</v>
+        <v>0.5137274405689024</v>
       </c>
       <c r="D96" t="n">
-        <v>0.2895369264292407</v>
+        <v>0.2895369264292396</v>
       </c>
       <c r="E96" t="n">
-        <v>0.4784092645959691</v>
+        <v>0.4784092645959666</v>
       </c>
       <c r="F96" t="n">
-        <v>0.7869088838078954</v>
+        <v>0.7869088838078693</v>
       </c>
     </row>
     <row r="97">
@@ -2557,19 +2557,19 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.7870737744003685</v>
+        <v>0.7870737744003684</v>
       </c>
       <c r="C97" t="n">
-        <v>0.5144652002212469</v>
+        <v>0.5144652002212471</v>
       </c>
       <c r="D97" t="n">
-        <v>0.2544639142709129</v>
+        <v>0.2544639142709116</v>
       </c>
       <c r="E97" t="n">
-        <v>0.4003898923537049</v>
+        <v>0.4003898923537028</v>
       </c>
       <c r="F97" t="n">
-        <v>0.7720579782106221</v>
+        <v>0.7720579782105965</v>
       </c>
     </row>
     <row r="98">
@@ -2579,19 +2579,19 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.7869954182490549</v>
+        <v>0.7869954182490553</v>
       </c>
       <c r="C98" t="n">
-        <v>0.5286012725862574</v>
+        <v>0.5286012725862581</v>
       </c>
       <c r="D98" t="n">
-        <v>0.1994740222460125</v>
+        <v>0.1994740222460115</v>
       </c>
       <c r="E98" t="n">
-        <v>0.3970769111301063</v>
+        <v>0.3970769111301053</v>
       </c>
       <c r="F98" t="n">
-        <v>0.8516001666601229</v>
+        <v>0.8516001666601143</v>
       </c>
     </row>
     <row r="99">
@@ -2601,19 +2601,19 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.8509197557535316</v>
+        <v>0.8509197557535314</v>
       </c>
       <c r="C99" t="n">
-        <v>0.4672140174498268</v>
+        <v>0.4672140174498279</v>
       </c>
       <c r="D99" t="n">
-        <v>0.05688077044704543</v>
+        <v>0.05688077044704434</v>
       </c>
       <c r="E99" t="n">
-        <v>0.3585331217240484</v>
+        <v>0.3585331217240506</v>
       </c>
       <c r="F99" t="n">
-        <v>0.8649330824721845</v>
+        <v>0.8649330824721809</v>
       </c>
     </row>
     <row r="100">
@@ -2623,19 +2623,19 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.7963922938986352</v>
+        <v>0.7963922938986353</v>
       </c>
       <c r="C100" t="n">
-        <v>0.2450370567411396</v>
+        <v>0.2450370567411391</v>
       </c>
       <c r="D100" t="n">
-        <v>0.2725582586420912</v>
+        <v>0.2725582586420934</v>
       </c>
       <c r="E100" t="n">
-        <v>0.7077428393800212</v>
+        <v>0.7077428393800224</v>
       </c>
       <c r="F100" t="n">
-        <v>0.7413032662185408</v>
+        <v>0.7413032662185203</v>
       </c>
     </row>
     <row r="101">
@@ -2648,16 +2648,16 @@
         <v>0.5806179609105648</v>
       </c>
       <c r="C101" t="n">
-        <v>0.05452068623464615</v>
+        <v>0.0545206862346467</v>
       </c>
       <c r="D101" t="n">
-        <v>0.2605738331484013</v>
+        <v>0.2605738331484016</v>
       </c>
       <c r="E101" t="n">
-        <v>0.4756543229863083</v>
+        <v>0.4756543229863029</v>
       </c>
       <c r="F101" t="n">
-        <v>0.7771696009376143</v>
+        <v>0.7771696009375836</v>
       </c>
     </row>
     <row r="102">
@@ -2667,19 +2667,19 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.8986836101388748</v>
+        <v>0.8986836101388749</v>
       </c>
       <c r="C102" t="n">
-        <v>0.3617484295284565</v>
+        <v>0.3617484295284554</v>
       </c>
       <c r="D102" t="n">
-        <v>0.4245616924366764</v>
+        <v>0.4245616924366789</v>
       </c>
       <c r="E102" t="n">
-        <v>0.8729031684808878</v>
+        <v>0.8729031684808901</v>
       </c>
       <c r="F102" t="n">
-        <v>0.7634849404491879</v>
+        <v>0.7634849404491747</v>
       </c>
     </row>
     <row r="103">
@@ -2689,19 +2689,19 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.9029626820114355</v>
+        <v>0.9029626820114356</v>
       </c>
       <c r="C103" t="n">
-        <v>0.3672863483682642</v>
+        <v>0.3672863483682631</v>
       </c>
       <c r="D103" t="n">
-        <v>0.4771591056542676</v>
+        <v>0.4771591056542704</v>
       </c>
       <c r="E103" t="n">
-        <v>0.8449152236591827</v>
+        <v>0.8449152236591846</v>
       </c>
       <c r="F103" t="n">
-        <v>0.7649706601198466</v>
+        <v>0.7649706601198334</v>
       </c>
     </row>
     <row r="104">
@@ -2711,19 +2711,19 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.6604721130227571</v>
+        <v>0.6604721130227572</v>
       </c>
       <c r="C104" t="n">
-        <v>0.1352533261246091</v>
+        <v>0.1352533261246092</v>
       </c>
       <c r="D104" t="n">
-        <v>0.291717177754278</v>
+        <v>0.2917171777542793</v>
       </c>
       <c r="E104" t="n">
-        <v>0.6084573974854596</v>
+        <v>0.6084573974854569</v>
       </c>
       <c r="F104" t="n">
-        <v>0.7596307370945014</v>
+        <v>0.7596307370944757</v>
       </c>
     </row>
     <row r="105">
@@ -2736,16 +2736,16 @@
         <v>0.8635404906893061</v>
       </c>
       <c r="C105" t="n">
-        <v>0.5496490061060924</v>
+        <v>0.549649006106092</v>
       </c>
       <c r="D105" t="n">
-        <v>0.2527972668890621</v>
+        <v>0.2527972668890638</v>
       </c>
       <c r="E105" t="n">
-        <v>0.6132510704223605</v>
+        <v>0.6132510704223618</v>
       </c>
       <c r="F105" t="n">
-        <v>0.766567008430367</v>
+        <v>0.7665670084303464</v>
       </c>
     </row>
     <row r="106">
@@ -2755,19 +2755,19 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.8229662016667797</v>
+        <v>0.8229662016667799</v>
       </c>
       <c r="C106" t="n">
-        <v>0.4083078764561028</v>
+        <v>0.4083078764561027</v>
       </c>
       <c r="D106" t="n">
-        <v>0.248928400251081</v>
+        <v>0.2489284002510819</v>
       </c>
       <c r="E106" t="n">
-        <v>0.5653055862778478</v>
+        <v>0.5653055862778481</v>
       </c>
       <c r="F106" t="n">
-        <v>0.7861667015733976</v>
+        <v>0.7861667015733803</v>
       </c>
     </row>
     <row r="107">
@@ -2777,19 +2777,19 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.8081628070761954</v>
+        <v>0.8081628070761957</v>
       </c>
       <c r="C107" t="n">
-        <v>0.3462768321976497</v>
+        <v>0.34627683219765</v>
       </c>
       <c r="D107" t="n">
-        <v>0.7668243955867005</v>
+        <v>0.7668243955866987</v>
       </c>
       <c r="E107" t="n">
-        <v>0.3867585462655442</v>
+        <v>0.3867585462655374</v>
       </c>
       <c r="F107" t="n">
-        <v>0.7761401227617475</v>
+        <v>0.7761401227617282</v>
       </c>
     </row>
     <row r="108">
@@ -2802,16 +2802,16 @@
         <v>0.7185982163075638</v>
       </c>
       <c r="C108" t="n">
-        <v>0.2547528039454141</v>
+        <v>0.2547528039454145</v>
       </c>
       <c r="D108" t="n">
-        <v>0.73798536279793</v>
+        <v>0.7379853627979274</v>
       </c>
       <c r="E108" t="n">
-        <v>0.3535254936242991</v>
+        <v>0.353525493624291</v>
       </c>
       <c r="F108" t="n">
-        <v>0.741221913767673</v>
+        <v>0.7412219137676503</v>
       </c>
     </row>
     <row r="109">
@@ -2824,16 +2824,16 @@
         <v>0.8800206359037155</v>
       </c>
       <c r="C109" t="n">
-        <v>0.3616511671995285</v>
+        <v>0.3616511671995273</v>
       </c>
       <c r="D109" t="n">
-        <v>0.3259444347480267</v>
+        <v>0.3259444347480298</v>
       </c>
       <c r="E109" t="n">
-        <v>0.8710695233885266</v>
+        <v>0.8710695233885293</v>
       </c>
       <c r="F109" t="n">
-        <v>0.7679358793520805</v>
+        <v>0.7679358793520664</v>
       </c>
     </row>
     <row r="110">
@@ -2843,19 +2843,19 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.8589992281275708</v>
+        <v>0.8589992281275709</v>
       </c>
       <c r="C110" t="n">
-        <v>0.3667072147791755</v>
+        <v>0.366707214779175</v>
       </c>
       <c r="D110" t="n">
-        <v>0.4466599697632456</v>
+        <v>0.4466599697632478</v>
       </c>
       <c r="E110" t="n">
-        <v>0.7842946891712416</v>
+        <v>0.7842946891712438</v>
       </c>
       <c r="F110" t="n">
-        <v>0.7777853360112154</v>
+        <v>0.7777853360112021</v>
       </c>
     </row>
     <row r="111">
@@ -2868,16 +2868,16 @@
         <v>0.5958160227235592</v>
       </c>
       <c r="C111" t="n">
-        <v>0.1412732853921832</v>
+        <v>0.1412732853921843</v>
       </c>
       <c r="D111" t="n">
-        <v>0.6191301838142772</v>
+        <v>0.6191301838142742</v>
       </c>
       <c r="E111" t="n">
-        <v>0.2371617331185633</v>
+        <v>0.2371617331185538</v>
       </c>
       <c r="F111" t="n">
-        <v>0.7526798366735525</v>
+        <v>0.7526798366735284</v>
       </c>
     </row>
     <row r="112">
@@ -2890,16 +2890,16 @@
         <v>0.713063906162661</v>
       </c>
       <c r="C112" t="n">
-        <v>0.2421977974764079</v>
+        <v>0.2421977974764083</v>
       </c>
       <c r="D112" t="n">
-        <v>0.1985731012343232</v>
+        <v>0.1985731012343234</v>
       </c>
       <c r="E112" t="n">
-        <v>0.5150238768920063</v>
+        <v>0.5150238768920046</v>
       </c>
       <c r="F112" t="n">
-        <v>0.7811147962397862</v>
+        <v>0.7811147962397672</v>
       </c>
     </row>
     <row r="113">
@@ -2909,19 +2909,19 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.6901202061914022</v>
+        <v>0.6901202061914024</v>
       </c>
       <c r="C113" t="n">
-        <v>0.3164041651393831</v>
+        <v>0.3164041651393842</v>
       </c>
       <c r="D113" t="n">
-        <v>0.6999705582727768</v>
+        <v>0.6999705582727731</v>
       </c>
       <c r="E113" t="n">
-        <v>0.2812387321626458</v>
+        <v>0.2812387321626377</v>
       </c>
       <c r="F113" t="n">
-        <v>0.7793181612813853</v>
+        <v>0.7793181612813657</v>
       </c>
     </row>
     <row r="114">
@@ -2931,19 +2931,19 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.8795966354979805</v>
+        <v>0.8795966354979804</v>
       </c>
       <c r="C114" t="n">
-        <v>0.7027048879784473</v>
+        <v>0.702704887978448</v>
       </c>
       <c r="D114" t="n">
-        <v>0.1195855174696889</v>
+        <v>0.1195855174696871</v>
       </c>
       <c r="E114" t="n">
-        <v>0.3028462819595023</v>
+        <v>0.3028462819595034</v>
       </c>
       <c r="F114" t="n">
-        <v>0.8722099564553513</v>
+        <v>0.8722099564553476</v>
       </c>
     </row>
     <row r="115">
@@ -2956,16 +2956,16 @@
         <v>0.724925037465719</v>
       </c>
       <c r="C115" t="n">
-        <v>0.3966113837449121</v>
+        <v>0.3966113837449129</v>
       </c>
       <c r="D115" t="n">
-        <v>0.6975783925029866</v>
+        <v>0.6975783925029835</v>
       </c>
       <c r="E115" t="n">
-        <v>0.2782073678759966</v>
+        <v>0.2782073678759884</v>
       </c>
       <c r="F115" t="n">
-        <v>0.7547534810808124</v>
+        <v>0.7547534810807893</v>
       </c>
     </row>
     <row r="116">
@@ -2975,19 +2975,19 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.6559119909203537</v>
+        <v>0.6559119909203535</v>
       </c>
       <c r="C116" t="n">
-        <v>0.2987393083621997</v>
+        <v>0.2987393083622008</v>
       </c>
       <c r="D116" t="n">
-        <v>0.6140923075810962</v>
+        <v>0.6140923075810928</v>
       </c>
       <c r="E116" t="n">
-        <v>0.2192778782936278</v>
+        <v>0.219277878293619</v>
       </c>
       <c r="F116" t="n">
-        <v>0.7202208047608475</v>
+        <v>0.7202208047608218</v>
       </c>
     </row>
     <row r="117">
@@ -2997,19 +2997,19 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.8184685791343226</v>
+        <v>0.8184685791343227</v>
       </c>
       <c r="C117" t="n">
-        <v>0.668140154337862</v>
+        <v>0.6681401543378614</v>
       </c>
       <c r="D117" t="n">
-        <v>0.346709717677099</v>
+        <v>0.3467097176771</v>
       </c>
       <c r="E117" t="n">
-        <v>0.6574951293314617</v>
+        <v>0.65749512933146</v>
       </c>
       <c r="F117" t="n">
-        <v>0.7543347642297638</v>
+        <v>0.7543347642297288</v>
       </c>
     </row>
     <row r="118">
@@ -3022,16 +3022,16 @@
         <v>0.7362175575364186</v>
       </c>
       <c r="C118" t="n">
-        <v>0.4187399035489053</v>
+        <v>0.4187399035489054</v>
       </c>
       <c r="D118" t="n">
-        <v>0.03076181651705337</v>
+        <v>0.03076181651705295</v>
       </c>
       <c r="E118" t="n">
-        <v>0.4596645676818807</v>
+        <v>0.45966456768188</v>
       </c>
       <c r="F118" t="n">
-        <v>0.7573025715459593</v>
+        <v>0.7573025715459333</v>
       </c>
     </row>
     <row r="119">
@@ -3041,19 +3041,19 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.7977996047016364</v>
+        <v>0.7977996047016365</v>
       </c>
       <c r="C119" t="n">
-        <v>0.6004403352538795</v>
+        <v>0.6004403352538787</v>
       </c>
       <c r="D119" t="n">
-        <v>0.41708868195814</v>
+        <v>0.417088681958141</v>
       </c>
       <c r="E119" t="n">
-        <v>0.6939393609296372</v>
+        <v>0.6939393609296353</v>
       </c>
       <c r="F119" t="n">
-        <v>0.756785513539685</v>
+        <v>0.7567855135396522</v>
       </c>
     </row>
     <row r="120">
@@ -3063,19 +3063,19 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.7660348887240495</v>
+        <v>0.7660348887240496</v>
       </c>
       <c r="C120" t="n">
-        <v>0.5312068270490027</v>
+        <v>0.5312068270490028</v>
       </c>
       <c r="D120" t="n">
-        <v>0.2101554424258901</v>
+        <v>0.2101554424258894</v>
       </c>
       <c r="E120" t="n">
-        <v>0.458831003374563</v>
+        <v>0.4588310033745598</v>
       </c>
       <c r="F120" t="n">
-        <v>0.7654939800535037</v>
+        <v>0.7654939800534707</v>
       </c>
     </row>
     <row r="121">
@@ -3085,19 +3085,19 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.8329378661766036</v>
+        <v>0.8329378661766037</v>
       </c>
       <c r="C121" t="n">
-        <v>0.4683583148851872</v>
+        <v>0.468358314885187</v>
       </c>
       <c r="D121" t="n">
-        <v>0.2949446644430228</v>
+        <v>0.2949446644430226</v>
       </c>
       <c r="E121" t="n">
-        <v>0.5747578710856969</v>
+        <v>0.5747578710856959</v>
       </c>
       <c r="F121" t="n">
-        <v>0.7532767274950967</v>
+        <v>0.7532767274950726</v>
       </c>
     </row>
     <row r="122">
@@ -3107,19 +3107,19 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.7467829688156998</v>
+        <v>0.7467829688156997</v>
       </c>
       <c r="C122" t="n">
         <v>0.547445971111882</v>
       </c>
       <c r="D122" t="n">
-        <v>0.1680703412224871</v>
+        <v>0.1680703412224867</v>
       </c>
       <c r="E122" t="n">
-        <v>0.4666233628704205</v>
+        <v>0.4666233628704184</v>
       </c>
       <c r="F122" t="n">
-        <v>0.7905296270674235</v>
+        <v>0.7905296270673976</v>
       </c>
     </row>
     <row r="123">
@@ -3129,19 +3129,19 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.7978344230221083</v>
+        <v>0.7978344230221085</v>
       </c>
       <c r="C123" t="n">
-        <v>0.6371751038521086</v>
+        <v>0.6371751038521088</v>
       </c>
       <c r="D123" t="n">
-        <v>0.2192882275382034</v>
+        <v>0.2192882275382023</v>
       </c>
       <c r="E123" t="n">
-        <v>0.3947845965331938</v>
+        <v>0.3947845965331914</v>
       </c>
       <c r="F123" t="n">
-        <v>0.7642033821521933</v>
+        <v>0.7642033821521631</v>
       </c>
     </row>
     <row r="124">
@@ -3154,16 +3154,16 @@
         <v>0.7592756502857615</v>
       </c>
       <c r="C124" t="n">
-        <v>0.499604496258839</v>
+        <v>0.4996044962588402</v>
       </c>
       <c r="D124" t="n">
-        <v>0.589338267412694</v>
+        <v>0.5893382674126897</v>
       </c>
       <c r="E124" t="n">
-        <v>0.1479216055655954</v>
+        <v>0.1479216055655882</v>
       </c>
       <c r="F124" t="n">
-        <v>0.7794304943670791</v>
+        <v>0.7794304943670572</v>
       </c>
     </row>
     <row r="125">
@@ -3173,19 +3173,19 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.7876856854517061</v>
+        <v>0.7876856854517063</v>
       </c>
       <c r="C125" t="n">
         <v>0.6445290672233389</v>
       </c>
       <c r="D125" t="n">
-        <v>0.139279634170175</v>
+        <v>0.1392796341701749</v>
       </c>
       <c r="E125" t="n">
-        <v>0.4648857124575154</v>
+        <v>0.4648857124575151</v>
       </c>
       <c r="F125" t="n">
-        <v>0.7697955793073462</v>
+        <v>0.7697955793073181</v>
       </c>
     </row>
     <row r="126">
@@ -3195,19 +3195,19 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.9883421682038442</v>
+        <v>0.9883421682038445</v>
       </c>
       <c r="C126" t="n">
-        <v>0.8255849425013204</v>
+        <v>0.8255849425013195</v>
       </c>
       <c r="D126" t="n">
-        <v>0.2876134683139494</v>
+        <v>0.2876134683139513</v>
       </c>
       <c r="E126" t="n">
-        <v>0.7043351599409778</v>
+        <v>0.7043351599409823</v>
       </c>
       <c r="F126" t="n">
-        <v>0.7002480290456883</v>
+        <v>0.7002480290456614</v>
       </c>
     </row>
     <row r="127">
@@ -3217,19 +3217,19 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.7562497650847783</v>
+        <v>0.7562497650847785</v>
       </c>
       <c r="C127" t="n">
-        <v>0.5108524526997933</v>
+        <v>0.5108524526997935</v>
       </c>
       <c r="D127" t="n">
-        <v>0.2997752398145623</v>
+        <v>0.2997752398145619</v>
       </c>
       <c r="E127" t="n">
-        <v>0.4998763970306422</v>
+        <v>0.4998763970306395</v>
       </c>
       <c r="F127" t="n">
-        <v>0.7650835024707142</v>
+        <v>0.7650835024706858</v>
       </c>
     </row>
     <row r="128">
@@ -3239,19 +3239,19 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.8221493647903242</v>
+        <v>0.8221493647903243</v>
       </c>
       <c r="C128" t="n">
-        <v>0.3658771178679248</v>
+        <v>0.3658771178679244</v>
       </c>
       <c r="D128" t="n">
-        <v>0.2676905128149104</v>
+        <v>0.2676905128149121</v>
       </c>
       <c r="E128" t="n">
-        <v>0.6793361382030534</v>
+        <v>0.6793361382030537</v>
       </c>
       <c r="F128" t="n">
-        <v>0.7592703835564769</v>
+        <v>0.7592703835564506</v>
       </c>
     </row>
     <row r="129">
@@ -3264,16 +3264,16 @@
         <v>0.7959455349799387</v>
       </c>
       <c r="C129" t="n">
-        <v>0.6545475538730884</v>
+        <v>0.6545475538730883</v>
       </c>
       <c r="D129" t="n">
-        <v>0.07534602287305264</v>
+        <v>0.07534602287305271</v>
       </c>
       <c r="E129" t="n">
-        <v>0.4587465732647811</v>
+        <v>0.4587465732647817</v>
       </c>
       <c r="F129" t="n">
-        <v>0.7653944899076379</v>
+        <v>0.7653944899076103</v>
       </c>
     </row>
     <row r="130">
@@ -3283,19 +3283,19 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.04395069323131195</v>
+        <v>0.04395069323131207</v>
       </c>
       <c r="C130" t="n">
-        <v>0.3740799030716127</v>
+        <v>0.3740799030716125</v>
       </c>
       <c r="D130" t="n">
-        <v>0.5254135980102925</v>
+        <v>0.5254135980102931</v>
       </c>
       <c r="E130" t="n">
-        <v>0.5630765559879559</v>
+        <v>0.5630765559879523</v>
       </c>
       <c r="F130" t="n">
-        <v>0.7267865351165865</v>
+        <v>0.7267865351165588</v>
       </c>
     </row>
     <row r="131">
@@ -3305,19 +3305,19 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.09346796760669869</v>
+        <v>0.09346796760669893</v>
       </c>
       <c r="C131" t="n">
-        <v>0.4485187043577988</v>
+        <v>0.4485187043577984</v>
       </c>
       <c r="D131" t="n">
-        <v>0.5065817351252817</v>
+        <v>0.506581735125283</v>
       </c>
       <c r="E131" t="n">
-        <v>0.5998018394910085</v>
+        <v>0.5998018394910072</v>
       </c>
       <c r="F131" t="n">
-        <v>0.7328455982932873</v>
+        <v>0.7328455982932618</v>
       </c>
     </row>
     <row r="132">
@@ -3327,19 +3327,19 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.09710082018846675</v>
+        <v>0.09710082018846708</v>
       </c>
       <c r="C132" t="n">
-        <v>0.5375925785741597</v>
+        <v>0.5375925785741584</v>
       </c>
       <c r="D132" t="n">
-        <v>0.5680123692237197</v>
+        <v>0.568012369223722</v>
       </c>
       <c r="E132" t="n">
-        <v>0.7805398761699857</v>
+        <v>0.7805398761699878</v>
       </c>
       <c r="F132" t="n">
-        <v>0.7494503464369919</v>
+        <v>0.7494503464369731</v>
       </c>
     </row>
     <row r="133">
@@ -3349,19 +3349,19 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.08176938192313848</v>
+        <v>0.08176938192313871</v>
       </c>
       <c r="C133" t="n">
-        <v>0.471742007152758</v>
+        <v>0.4717420071527567</v>
       </c>
       <c r="D133" t="n">
-        <v>0.5744526237647916</v>
+        <v>0.5744526237647938</v>
       </c>
       <c r="E133" t="n">
-        <v>0.8008599224994778</v>
+        <v>0.8008599224994787</v>
       </c>
       <c r="F133" t="n">
-        <v>0.7288528011600128</v>
+        <v>0.7288528011599907</v>
       </c>
     </row>
     <row r="134">
@@ -3371,19 +3371,19 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.1211328757567303</v>
+        <v>0.1211328757567305</v>
       </c>
       <c r="C134" t="n">
-        <v>0.6254609881448399</v>
+        <v>0.6254609881448377</v>
       </c>
       <c r="D134" t="n">
-        <v>0.6979883433642814</v>
+        <v>0.6979883433642842</v>
       </c>
       <c r="E134" t="n">
-        <v>0.9159193317549634</v>
+        <v>0.9159193317549666</v>
       </c>
       <c r="F134" t="n">
-        <v>0.7377116200541417</v>
+        <v>0.7377116200541233</v>
       </c>
     </row>
     <row r="135">
@@ -3393,19 +3393,19 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.05090709626976139</v>
+        <v>0.0509070962697615</v>
       </c>
       <c r="C135" t="n">
-        <v>0.2993740994349465</v>
+        <v>0.2993740994349464</v>
       </c>
       <c r="D135" t="n">
-        <v>0.4758097406153987</v>
+        <v>0.4758097406153995</v>
       </c>
       <c r="E135" t="n">
-        <v>0.5529973414071528</v>
+        <v>0.5529973414071493</v>
       </c>
       <c r="F135" t="n">
-        <v>0.7684249036338845</v>
+        <v>0.768424903633857</v>
       </c>
     </row>
     <row r="136">
@@ -3415,19 +3415,19 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.06543026625794343</v>
+        <v>0.06543026625794371</v>
       </c>
       <c r="C136" t="n">
-        <v>0.3748656209838607</v>
+        <v>0.37486562098386</v>
       </c>
       <c r="D136" t="n">
-        <v>0.5268234698791382</v>
+        <v>0.5268234698791405</v>
       </c>
       <c r="E136" t="n">
-        <v>0.7199943752217828</v>
+        <v>0.7199943752217822</v>
       </c>
       <c r="F136" t="n">
-        <v>0.7348736095265596</v>
+        <v>0.7348736095265354</v>
       </c>
     </row>
     <row r="137">
@@ -3437,19 +3437,19 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.1310307570800351</v>
+        <v>0.1310307570800353</v>
       </c>
       <c r="C137" t="n">
-        <v>0.5395004259434861</v>
+        <v>0.5395004259434849</v>
       </c>
       <c r="D137" t="n">
-        <v>0.6592749865713029</v>
+        <v>0.6592749865713049</v>
       </c>
       <c r="E137" t="n">
-        <v>0.738660892458229</v>
+        <v>0.7386608924582291</v>
       </c>
       <c r="F137" t="n">
-        <v>0.7658930592352403</v>
+        <v>0.7658930592352232</v>
       </c>
     </row>
     <row r="138">
@@ -3459,19 +3459,19 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.08605555520448149</v>
+        <v>0.08605555520448184</v>
       </c>
       <c r="C138" t="n">
-        <v>0.5461874913049068</v>
+        <v>0.5461874913049055</v>
       </c>
       <c r="D138" t="n">
-        <v>0.6985761678497043</v>
+        <v>0.6985761678497061</v>
       </c>
       <c r="E138" t="n">
-        <v>0.7803684850665997</v>
+        <v>0.7803684850666004</v>
       </c>
       <c r="F138" t="n">
-        <v>0.7353788156774286</v>
+        <v>0.7353788156774059</v>
       </c>
     </row>
     <row r="139">
@@ -3481,19 +3481,19 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.05264612213277262</v>
+        <v>0.05264612213277273</v>
       </c>
       <c r="C139" t="n">
-        <v>0.3493229290876488</v>
+        <v>0.3493229290876479</v>
       </c>
       <c r="D139" t="n">
-        <v>0.5221391959316287</v>
+        <v>0.5221391959316295</v>
       </c>
       <c r="E139" t="n">
-        <v>0.6648126970419328</v>
+        <v>0.6648126970419312</v>
       </c>
       <c r="F139" t="n">
-        <v>0.7220389212519733</v>
+        <v>0.7220389212519513</v>
       </c>
     </row>
     <row r="140">
@@ -3503,19 +3503,19 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.1556009722383281</v>
+        <v>0.1556009722383283</v>
       </c>
       <c r="C140" t="n">
-        <v>0.5693619812284695</v>
+        <v>0.569361981228469</v>
       </c>
       <c r="D140" t="n">
-        <v>0.5405465268285065</v>
+        <v>0.5405465268285073</v>
       </c>
       <c r="E140" t="n">
-        <v>0.6124189897364718</v>
+        <v>0.6124189897364725</v>
       </c>
       <c r="F140" t="n">
-        <v>0.822113991296051</v>
+        <v>0.8221139912960441</v>
       </c>
     </row>
     <row r="141">
@@ -3525,19 +3525,19 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.0718973733311937</v>
+        <v>0.07189737333119373</v>
       </c>
       <c r="C141" t="n">
-        <v>0.449873194579319</v>
+        <v>0.4498731945793182</v>
       </c>
       <c r="D141" t="n">
-        <v>0.4609297578844608</v>
+        <v>0.4609297578844617</v>
       </c>
       <c r="E141" t="n">
-        <v>0.646773035332148</v>
+        <v>0.6467730353321495</v>
       </c>
       <c r="F141" t="n">
-        <v>0.7101474565016138</v>
+        <v>0.7101474565015923</v>
       </c>
     </row>
     <row r="142">
@@ -3547,19 +3547,19 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.1224662989239515</v>
+        <v>0.1224662989239518</v>
       </c>
       <c r="C142" t="n">
-        <v>0.6283328196179908</v>
+        <v>0.6283328196179893</v>
       </c>
       <c r="D142" t="n">
-        <v>0.597630673630777</v>
+        <v>0.5976306736307796</v>
       </c>
       <c r="E142" t="n">
-        <v>0.8322503901064663</v>
+        <v>0.8322503901064702</v>
       </c>
       <c r="F142" t="n">
-        <v>0.7723569373315452</v>
+        <v>0.7723569373315315</v>
       </c>
     </row>
     <row r="143">
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.158537269933985</v>
+        <v>0.1585372699339851</v>
       </c>
       <c r="C143" t="n">
-        <v>0.5727415519641119</v>
+        <v>0.5727415519641116</v>
       </c>
       <c r="D143" t="n">
-        <v>0.4645768332513806</v>
+        <v>0.4645768332513817</v>
       </c>
       <c r="E143" t="n">
-        <v>0.5580684534064961</v>
+        <v>0.558068453406497</v>
       </c>
       <c r="F143" t="n">
-        <v>0.858781248342395</v>
+        <v>0.8587812483423953</v>
       </c>
     </row>
     <row r="144">
@@ -3591,19 +3591,19 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.02701921213586776</v>
+        <v>0.02701921213586781</v>
       </c>
       <c r="C144" t="n">
-        <v>0.2355832008972799</v>
+        <v>0.2355832008972805</v>
       </c>
       <c r="D144" t="n">
-        <v>0.3132988657003868</v>
+        <v>0.3132988657003874</v>
       </c>
       <c r="E144" t="n">
-        <v>0.4801120856946923</v>
+        <v>0.48011208569469</v>
       </c>
       <c r="F144" t="n">
-        <v>0.7575775470279236</v>
+        <v>0.7575775470279023</v>
       </c>
     </row>
     <row r="145">
@@ -3613,19 +3613,19 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.1470286920606759</v>
+        <v>0.1470286920606761</v>
       </c>
       <c r="C145" t="n">
-        <v>0.618992981281404</v>
+        <v>0.6189929812814037</v>
       </c>
       <c r="D145" t="n">
-        <v>0.5528987139613853</v>
+        <v>0.5528987139613862</v>
       </c>
       <c r="E145" t="n">
-        <v>0.6048882552929159</v>
+        <v>0.6048882552929171</v>
       </c>
       <c r="F145" t="n">
-        <v>0.8379876008936572</v>
+        <v>0.8379876008936531</v>
       </c>
     </row>
     <row r="146">
@@ -3635,19 +3635,19 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.01651844788717561</v>
+        <v>0.01651844788717572</v>
       </c>
       <c r="C146" t="n">
-        <v>0.1578906181815685</v>
+        <v>0.157890618181569</v>
       </c>
       <c r="D146" t="n">
-        <v>0.3665334988457971</v>
+        <v>0.3665334988457968</v>
       </c>
       <c r="E146" t="n">
-        <v>0.3899430939084507</v>
+        <v>0.3899430939084476</v>
       </c>
       <c r="F146" t="n">
-        <v>0.853163131478451</v>
+        <v>0.8531631314784356</v>
       </c>
     </row>
     <row r="147">
@@ -3657,19 +3657,19 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.05943907128143181</v>
+        <v>0.05943907128143183</v>
       </c>
       <c r="C147" t="n">
-        <v>0.3892713650856102</v>
+        <v>0.3892713650856107</v>
       </c>
       <c r="D147" t="n">
-        <v>0.3996388947983849</v>
+        <v>0.3996388947983843</v>
       </c>
       <c r="E147" t="n">
-        <v>0.4061561138190322</v>
+        <v>0.4061561138190293</v>
       </c>
       <c r="F147" t="n">
-        <v>0.7645011837091532</v>
+        <v>0.7645011837091323</v>
       </c>
     </row>
     <row r="148">
@@ -3682,16 +3682,16 @@
         <v>0.1147644815973493</v>
       </c>
       <c r="C148" t="n">
-        <v>0.6771190253649135</v>
+        <v>0.6771190253649136</v>
       </c>
       <c r="D148" t="n">
-        <v>0.4546486677326624</v>
+        <v>0.4546486677326615</v>
       </c>
       <c r="E148" t="n">
-        <v>0.4462856887565372</v>
+        <v>0.4462856887565348</v>
       </c>
       <c r="F148" t="n">
-        <v>0.7678622487583343</v>
+        <v>0.7678622487583104</v>
       </c>
     </row>
     <row r="149">
@@ -3701,19 +3701,19 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.07702989392856378</v>
+        <v>0.07702989392856391</v>
       </c>
       <c r="C149" t="n">
-        <v>0.418780590786769</v>
+        <v>0.4187805907867692</v>
       </c>
       <c r="D149" t="n">
-        <v>0.4685261351740602</v>
+        <v>0.4685261351740599</v>
       </c>
       <c r="E149" t="n">
-        <v>0.4810653704918655</v>
+        <v>0.481065370491863</v>
       </c>
       <c r="F149" t="n">
-        <v>0.7593949325580015</v>
+        <v>0.75939493255798</v>
       </c>
     </row>
     <row r="150">
@@ -3723,19 +3723,19 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.05525197496775196</v>
+        <v>0.05525197496775219</v>
       </c>
       <c r="C150" t="n">
-        <v>0.3130779440544501</v>
+        <v>0.3130779440544497</v>
       </c>
       <c r="D150" t="n">
-        <v>0.4389303955002141</v>
+        <v>0.4389303955002152</v>
       </c>
       <c r="E150" t="n">
-        <v>0.6127963618207402</v>
+        <v>0.6127963618207372</v>
       </c>
       <c r="F150" t="n">
-        <v>0.747855832197017</v>
+        <v>0.747855832196989</v>
       </c>
     </row>
     <row r="151">
@@ -3745,19 +3745,19 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.09250349181995705</v>
+        <v>0.09250349181995712</v>
       </c>
       <c r="C151" t="n">
-        <v>0.3160827134977365</v>
+        <v>0.3160827134977369</v>
       </c>
       <c r="D151" t="n">
-        <v>0.5018148319582668</v>
+        <v>0.501814831958266</v>
       </c>
       <c r="E151" t="n">
-        <v>0.4035367458895091</v>
+        <v>0.4035367458895057</v>
       </c>
       <c r="F151" t="n">
-        <v>0.7782750324322555</v>
+        <v>0.7782750324322387</v>
       </c>
     </row>
     <row r="152">
@@ -3767,19 +3767,19 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.09311280618292322</v>
+        <v>0.09311280618292335</v>
       </c>
       <c r="C152" t="n">
-        <v>0.3924576646724449</v>
+        <v>0.3924576646724451</v>
       </c>
       <c r="D152" t="n">
-        <v>0.3536603046516154</v>
+        <v>0.353660304651616</v>
       </c>
       <c r="E152" t="n">
-        <v>0.5118631859189905</v>
+        <v>0.5118631859189908</v>
       </c>
       <c r="F152" t="n">
-        <v>0.8342552096011261</v>
+        <v>0.8342552096011164</v>
       </c>
     </row>
     <row r="153">
@@ -3792,16 +3792,16 @@
         <v>0.118113556474386</v>
       </c>
       <c r="C153" t="n">
-        <v>0.5341669546497618</v>
+        <v>0.5341669546497615</v>
       </c>
       <c r="D153" t="n">
-        <v>0.3428998131338691</v>
+        <v>0.3428998131338685</v>
       </c>
       <c r="E153" t="n">
-        <v>0.4584191222904871</v>
+        <v>0.4584191222904891</v>
       </c>
       <c r="F153" t="n">
-        <v>0.8699401247502841</v>
+        <v>0.8699401247502757</v>
       </c>
     </row>
     <row r="154">
@@ -3811,19 +3811,19 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.04707094945779024</v>
+        <v>0.04707094945779041</v>
       </c>
       <c r="C154" t="n">
-        <v>0.345150110941748</v>
+        <v>0.3451501109417477</v>
       </c>
       <c r="D154" t="n">
-        <v>0.3816356788167869</v>
+        <v>0.3816356788167886</v>
       </c>
       <c r="E154" t="n">
-        <v>0.6243470971922199</v>
+        <v>0.6243470971922206</v>
       </c>
       <c r="F154" t="n">
-        <v>0.777187420606018</v>
+        <v>0.7771874206059992</v>
       </c>
     </row>
     <row r="155">
@@ -3833,19 +3833,19 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.09917356752439405</v>
+        <v>0.09917356752439428</v>
       </c>
       <c r="C155" t="n">
-        <v>0.4680545968645693</v>
+        <v>0.4680545968645688</v>
       </c>
       <c r="D155" t="n">
-        <v>0.4935456244398753</v>
+        <v>0.4935456244398762</v>
       </c>
       <c r="E155" t="n">
-        <v>0.5849605861599005</v>
+        <v>0.5849605861598998</v>
       </c>
       <c r="F155" t="n">
-        <v>0.77563723574279</v>
+        <v>0.7756372357427688</v>
       </c>
     </row>
     <row r="156">
@@ -3855,19 +3855,19 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.08536212707055921</v>
+        <v>0.08536212707055944</v>
       </c>
       <c r="C156" t="n">
-        <v>0.4833435170647044</v>
+        <v>0.4833435170647041</v>
       </c>
       <c r="D156" t="n">
-        <v>0.4925238140468168</v>
+        <v>0.4925238140468174</v>
       </c>
       <c r="E156" t="n">
-        <v>0.5608733858817585</v>
+        <v>0.5608733858817587</v>
       </c>
       <c r="F156" t="n">
-        <v>0.8031547643633817</v>
+        <v>0.8031547643633643</v>
       </c>
     </row>
     <row r="157">
@@ -3877,19 +3877,19 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.0229405052102219</v>
+        <v>0.02294050521022201</v>
       </c>
       <c r="C157" t="n">
-        <v>0.2838614596648464</v>
+        <v>0.2838614596648466</v>
       </c>
       <c r="D157" t="n">
-        <v>0.4693421910089521</v>
+        <v>0.4693421910089526</v>
       </c>
       <c r="E157" t="n">
-        <v>0.5283810787222338</v>
+        <v>0.5283810787222308</v>
       </c>
       <c r="F157" t="n">
-        <v>0.7817792133498069</v>
+        <v>0.7817792133497845</v>
       </c>
     </row>
     <row r="158">
@@ -3899,19 +3899,19 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.01558759115419757</v>
+        <v>0.01558759115419768</v>
       </c>
       <c r="C158" t="n">
-        <v>0.2724803175743026</v>
+        <v>0.2724803175743031</v>
       </c>
       <c r="D158" t="n">
-        <v>0.4293049574685316</v>
+        <v>0.4293049574685318</v>
       </c>
       <c r="E158" t="n">
-        <v>0.4961221289987257</v>
+        <v>0.4961221289987226</v>
       </c>
       <c r="F158" t="n">
-        <v>0.7794902405362458</v>
+        <v>0.7794902405362228</v>
       </c>
     </row>
     <row r="159">
@@ -3921,19 +3921,19 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.03387466480255315</v>
+        <v>0.03387466480255331</v>
       </c>
       <c r="C159" t="n">
-        <v>0.3604844254473762</v>
+        <v>0.3604844254473763</v>
       </c>
       <c r="D159" t="n">
-        <v>0.4834608643750656</v>
+        <v>0.4834608643750657</v>
       </c>
       <c r="E159" t="n">
-        <v>0.5187389044805205</v>
+        <v>0.518738904480518</v>
       </c>
       <c r="F159" t="n">
-        <v>0.7855032943403888</v>
+        <v>0.785503294340368</v>
       </c>
     </row>
     <row r="160">
@@ -3943,19 +3943,19 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.03478323836070961</v>
+        <v>0.03478323836070978</v>
       </c>
       <c r="C160" t="n">
-        <v>0.3644347415099093</v>
+        <v>0.3644347415099086</v>
       </c>
       <c r="D160" t="n">
-        <v>0.3199383979869654</v>
+        <v>0.3199383979869678</v>
       </c>
       <c r="E160" t="n">
-        <v>0.7393662319470747</v>
+        <v>0.7393662319470771</v>
       </c>
       <c r="F160" t="n">
-        <v>0.7686823104148548</v>
+        <v>0.768682310414836</v>
       </c>
     </row>
     <row r="161">
@@ -3965,19 +3965,19 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.05122793612260153</v>
+        <v>0.05122793612260165</v>
       </c>
       <c r="C161" t="n">
-        <v>0.3030761434879954</v>
+        <v>0.3030761434879958</v>
       </c>
       <c r="D161" t="n">
-        <v>0.3050634668767417</v>
+        <v>0.3050634668767422</v>
       </c>
       <c r="E161" t="n">
-        <v>0.4686750031933798</v>
+        <v>0.4686750031933783</v>
       </c>
       <c r="F161" t="n">
-        <v>0.8209550736379997</v>
+        <v>0.8209550736379811</v>
       </c>
     </row>
     <row r="162">
@@ -3987,19 +3987,19 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.06252094048705266</v>
+        <v>0.06252094048705278</v>
       </c>
       <c r="C162" t="n">
-        <v>0.376268785718373</v>
+        <v>0.3762687857183732</v>
       </c>
       <c r="D162" t="n">
-        <v>0.3188981650485752</v>
+        <v>0.3188981650485761</v>
       </c>
       <c r="E162" t="n">
-        <v>0.5199168562887122</v>
+        <v>0.5199168562887112</v>
       </c>
       <c r="F162" t="n">
-        <v>0.7865129731165749</v>
+        <v>0.7865129731165589</v>
       </c>
     </row>
     <row r="163">
@@ -4009,19 +4009,19 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.06566813862225833</v>
+        <v>0.06566813862225834</v>
       </c>
       <c r="C163" t="n">
-        <v>0.2447218192794038</v>
+        <v>0.2447218192794047</v>
       </c>
       <c r="D163" t="n">
-        <v>0.2596873827508431</v>
+        <v>0.2596873827508425</v>
       </c>
       <c r="E163" t="n">
-        <v>0.3714250815256019</v>
+        <v>0.3714250815255997</v>
       </c>
       <c r="F163" t="n">
-        <v>0.8345015856299433</v>
+        <v>0.8345015856299335</v>
       </c>
     </row>
     <row r="164">
@@ -4031,19 +4031,19 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.04803500167869649</v>
+        <v>0.0480350016786965</v>
       </c>
       <c r="C164" t="n">
-        <v>0.2672869680027662</v>
+        <v>0.2672869680027667</v>
       </c>
       <c r="D164" t="n">
-        <v>0.2610227406480929</v>
+        <v>0.2610227406480935</v>
       </c>
       <c r="E164" t="n">
-        <v>0.4541404404098625</v>
+        <v>0.4541404404098609</v>
       </c>
       <c r="F164" t="n">
-        <v>0.7532849655495906</v>
+        <v>0.7532849655495687</v>
       </c>
     </row>
     <row r="165">
@@ -4053,19 +4053,19 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.03318506723061337</v>
+        <v>0.03318506723061348</v>
       </c>
       <c r="C165" t="n">
-        <v>0.2842373298221766</v>
+        <v>0.284237329822177</v>
       </c>
       <c r="D165" t="n">
-        <v>0.3248312611998282</v>
+        <v>0.3248312611998296</v>
       </c>
       <c r="E165" t="n">
-        <v>0.5718366519974567</v>
+        <v>0.571836651997456</v>
       </c>
       <c r="F165" t="n">
-        <v>0.7834007645021511</v>
+        <v>0.7834007645021328</v>
       </c>
     </row>
     <row r="166">
@@ -4078,16 +4078,16 @@
         <v>0.02315212411980686</v>
       </c>
       <c r="C166" t="n">
-        <v>0.2072278419822174</v>
+        <v>0.2072278419822181</v>
       </c>
       <c r="D166" t="n">
-        <v>0.2312276611548861</v>
+        <v>0.2312276611548863</v>
       </c>
       <c r="E166" t="n">
-        <v>0.4170666660959896</v>
+        <v>0.4170666660959882</v>
       </c>
       <c r="F166" t="n">
-        <v>0.7984596839963002</v>
+        <v>0.7984596839962849</v>
       </c>
     </row>
     <row r="167">
@@ -4097,19 +4097,19 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.08611923666280757</v>
+        <v>0.0861192366628078</v>
       </c>
       <c r="C167" t="n">
-        <v>0.4739828842891006</v>
+        <v>0.4739828842890996</v>
       </c>
       <c r="D167" t="n">
-        <v>0.5268722085117434</v>
+        <v>0.5268722085117464</v>
       </c>
       <c r="E167" t="n">
-        <v>0.8192020352280635</v>
+        <v>0.819202035228065</v>
       </c>
       <c r="F167" t="n">
-        <v>0.7208527979007374</v>
+        <v>0.7208527979007135</v>
       </c>
     </row>
     <row r="168">
@@ -4119,19 +4119,19 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.1376833123767818</v>
+        <v>0.1376833123767821</v>
       </c>
       <c r="C168" t="n">
-        <v>0.6635403233428966</v>
+        <v>0.663540323342896</v>
       </c>
       <c r="D168" t="n">
-        <v>0.5554257160945191</v>
+        <v>0.5554257160945207</v>
       </c>
       <c r="E168" t="n">
-        <v>0.6509512559768764</v>
+        <v>0.6509512559768783</v>
       </c>
       <c r="F168" t="n">
-        <v>0.8564766731418307</v>
+        <v>0.8564766731418278</v>
       </c>
     </row>
     <row r="169">
@@ -4141,19 +4141,19 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.05173980978529644</v>
+        <v>0.05173980978529655</v>
       </c>
       <c r="C169" t="n">
-        <v>0.2787841941996736</v>
+        <v>0.2787841941996737</v>
       </c>
       <c r="D169" t="n">
-        <v>0.1775847093137396</v>
+        <v>0.1775847093137409</v>
       </c>
       <c r="E169" t="n">
-        <v>0.5636709782005731</v>
+        <v>0.5636709782005745</v>
       </c>
       <c r="F169" t="n">
-        <v>0.7838647818706351</v>
+        <v>0.7838647818706191</v>
       </c>
     </row>
     <row r="170">
@@ -4163,19 +4163,19 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.06618940870364687</v>
+        <v>0.06618940870364699</v>
       </c>
       <c r="C170" t="n">
-        <v>0.3622100192015862</v>
+        <v>0.3622100192015861</v>
       </c>
       <c r="D170" t="n">
-        <v>0.2697378442222584</v>
+        <v>0.2697378442222595</v>
       </c>
       <c r="E170" t="n">
-        <v>0.5501888580310911</v>
+        <v>0.5501888580310915</v>
       </c>
       <c r="F170" t="n">
-        <v>0.7712575259507952</v>
+        <v>0.7712575259507783</v>
       </c>
     </row>
     <row r="171">
@@ -4185,16 +4185,16 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.05467973033282472</v>
+        <v>0.05467973033282484</v>
       </c>
       <c r="C171" t="n">
-        <v>0.3798576114781817</v>
+        <v>0.3798576114781811</v>
       </c>
       <c r="D171" t="n">
-        <v>0.3836718802633206</v>
+        <v>0.3836718802633208</v>
       </c>
       <c r="E171" t="n">
-        <v>0.603420783414554</v>
+        <v>0.6034207834145559</v>
       </c>
       <c r="F171" t="n">
         <v>1</v>
@@ -4207,19 +4207,19 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.04262117176730232</v>
+        <v>0.04262117176730227</v>
       </c>
       <c r="C172" t="n">
-        <v>0.3722074343631919</v>
+        <v>0.3722074343631925</v>
       </c>
       <c r="D172" t="n">
         <v>0.3108373870913209</v>
       </c>
       <c r="E172" t="n">
-        <v>0.4441512468924999</v>
+        <v>0.4441512468924995</v>
       </c>
       <c r="F172" t="n">
-        <v>0.7682952352909462</v>
+        <v>0.7682952352909285</v>
       </c>
     </row>
     <row r="173">
@@ -4229,19 +4229,19 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.02733522197701397</v>
+        <v>0.02733522197701403</v>
       </c>
       <c r="C173" t="n">
-        <v>0.2420888291684618</v>
+        <v>0.2420888291684622</v>
       </c>
       <c r="D173" t="n">
-        <v>0.2906721518277802</v>
+        <v>0.2906721518277808</v>
       </c>
       <c r="E173" t="n">
-        <v>0.4942632164696371</v>
+        <v>0.4942632164696361</v>
       </c>
       <c r="F173" t="n">
-        <v>0.7853366457402867</v>
+        <v>0.78533664574027</v>
       </c>
     </row>
     <row r="174">
@@ -4254,16 +4254,16 @@
         <v>0</v>
       </c>
       <c r="C174" t="n">
-        <v>0.130652678917333</v>
+        <v>0.1306526789173341</v>
       </c>
       <c r="D174" t="n">
-        <v>0.2515105304487057</v>
+        <v>0.2515105304487051</v>
       </c>
       <c r="E174" t="n">
-        <v>0.3363453679776783</v>
+        <v>0.3363453679776752</v>
       </c>
       <c r="F174" t="n">
-        <v>0.7820281241707727</v>
+        <v>0.7820281241707561</v>
       </c>
     </row>
     <row r="175">
@@ -4273,19 +4273,19 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.01324083181406626</v>
+        <v>0.01324083181406627</v>
       </c>
       <c r="C175" t="n">
-        <v>0.2531283263579013</v>
+        <v>0.2531283263579017</v>
       </c>
       <c r="D175" t="n">
-        <v>0.3230717908523138</v>
+        <v>0.3230717908523147</v>
       </c>
       <c r="E175" t="n">
-        <v>0.5299317225188234</v>
+        <v>0.529931722518822</v>
       </c>
       <c r="F175" t="n">
-        <v>0.7579802375748784</v>
+        <v>0.7579802375748559</v>
       </c>
     </row>
     <row r="176">
@@ -4295,19 +4295,19 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.1196883467659056</v>
+        <v>0.1196883467659057</v>
       </c>
       <c r="C176" t="n">
-        <v>0.3569195086440028</v>
+        <v>0.3569195086440032</v>
       </c>
       <c r="D176" t="n">
-        <v>0.4046786650277794</v>
+        <v>0.4046786650277795</v>
       </c>
       <c r="E176" t="n">
-        <v>0.4563399030188157</v>
+        <v>0.4563399030188126</v>
       </c>
       <c r="F176" t="n">
-        <v>0.8005894911318212</v>
+        <v>0.8005894911318003</v>
       </c>
     </row>
     <row r="177">
@@ -4317,19 +4317,19 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.1020384447189551</v>
+        <v>0.1020384447189552</v>
       </c>
       <c r="C177" t="n">
-        <v>0.3459058249012777</v>
+        <v>0.3459058249012779</v>
       </c>
       <c r="D177" t="n">
-        <v>0.4114810464267618</v>
+        <v>0.4114810464267623</v>
       </c>
       <c r="E177" t="n">
-        <v>0.4847582931184014</v>
+        <v>0.4847582931184002</v>
       </c>
       <c r="F177" t="n">
-        <v>0.8088082574340806</v>
+        <v>0.8088082574340685</v>
       </c>
     </row>
     <row r="178">
@@ -4339,19 +4339,19 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.06537351007835343</v>
+        <v>0.06537351007835361</v>
       </c>
       <c r="C178" t="n">
-        <v>0.3458060061876621</v>
+        <v>0.3458060061876619</v>
       </c>
       <c r="D178" t="n">
-        <v>0.4688578110675694</v>
+        <v>0.4688578110675703</v>
       </c>
       <c r="E178" t="n">
-        <v>0.579362667662772</v>
+        <v>0.5793626676627697</v>
       </c>
       <c r="F178" t="n">
-        <v>0.7634598980236431</v>
+        <v>0.7634598980236221</v>
       </c>
     </row>
     <row r="179">
@@ -4361,19 +4361,19 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.04942919239643196</v>
+        <v>0.04942919239643218</v>
       </c>
       <c r="C179" t="n">
-        <v>0.4192502695025004</v>
+        <v>0.4192502695024998</v>
       </c>
       <c r="D179" t="n">
-        <v>0.5057405833906989</v>
+        <v>0.5057405833907002</v>
       </c>
       <c r="E179" t="n">
-        <v>0.6265664763582967</v>
+        <v>0.6265664763582953</v>
       </c>
       <c r="F179" t="n">
-        <v>0.730748592417698</v>
+        <v>0.7307485924176724</v>
       </c>
     </row>
     <row r="180">
@@ -4383,19 +4383,19 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.04959949990975932</v>
+        <v>0.04959949990975954</v>
       </c>
       <c r="C180" t="n">
-        <v>0.3729375313755657</v>
+        <v>0.3729375313755656</v>
       </c>
       <c r="D180" t="n">
-        <v>0.4956326160807973</v>
+        <v>0.4956326160807988</v>
       </c>
       <c r="E180" t="n">
-        <v>0.6076430189638843</v>
+        <v>0.607643018963882</v>
       </c>
       <c r="F180" t="n">
-        <v>0.7385479581775046</v>
+        <v>0.73854795817748</v>
       </c>
     </row>
     <row r="181">
@@ -4405,19 +4405,19 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.07175929050125998</v>
+        <v>0.07175929050126011</v>
       </c>
       <c r="C181" t="n">
-        <v>0.4100126267939684</v>
+        <v>0.4100126267939683</v>
       </c>
       <c r="D181" t="n">
-        <v>0.4827142135250313</v>
+        <v>0.4827142135250319</v>
       </c>
       <c r="E181" t="n">
-        <v>0.5645428904331969</v>
+        <v>0.5645428904331951</v>
       </c>
       <c r="F181" t="n">
-        <v>0.7391011494934038</v>
+        <v>0.7391011494933794</v>
       </c>
     </row>
     <row r="182">
@@ -4427,19 +4427,19 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.08143172907642933</v>
+        <v>0.08143172907642951</v>
       </c>
       <c r="C182" t="n">
-        <v>0.4933552700621117</v>
+        <v>0.4933552700621111</v>
       </c>
       <c r="D182" t="n">
-        <v>0.5072221316218192</v>
+        <v>0.5072221316218204</v>
       </c>
       <c r="E182" t="n">
-        <v>0.6069338473470526</v>
+        <v>0.606933847347052</v>
       </c>
       <c r="F182" t="n">
-        <v>0.737030646487857</v>
+        <v>0.7370306464878329</v>
       </c>
     </row>
     <row r="183">
@@ -4449,19 +4449,19 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.07618006778661617</v>
+        <v>0.07618006778661644</v>
       </c>
       <c r="C183" t="n">
-        <v>0.4955277372763728</v>
+        <v>0.4955277372763721</v>
       </c>
       <c r="D183" t="n">
-        <v>0.5933914081542047</v>
+        <v>0.5933914081542059</v>
       </c>
       <c r="E183" t="n">
-        <v>0.6812420040367233</v>
+        <v>0.681242004036722</v>
       </c>
       <c r="F183" t="n">
-        <v>0.7374311839218449</v>
+        <v>0.7374311839218204</v>
       </c>
     </row>
     <row r="184">
@@ -4471,19 +4471,19 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.05969508373658943</v>
+        <v>0.05969508373658955</v>
       </c>
       <c r="C184" t="n">
-        <v>0.4153009819245612</v>
+        <v>0.415300981924561</v>
       </c>
       <c r="D184" t="n">
-        <v>0.5147116184096526</v>
+        <v>0.5147116184096536</v>
       </c>
       <c r="E184" t="n">
-        <v>0.6025865508303917</v>
+        <v>0.6025865508303893</v>
       </c>
       <c r="F184" t="n">
-        <v>0.7426402434019763</v>
+        <v>0.7426402434019506</v>
       </c>
     </row>
     <row r="185">
@@ -4493,19 +4493,19 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.09315896716217852</v>
+        <v>0.09315896716217868</v>
       </c>
       <c r="C185" t="n">
-        <v>0.4431927716744396</v>
+        <v>0.4431927716744398</v>
       </c>
       <c r="D185" t="n">
-        <v>0.4813602452155039</v>
+        <v>0.4813602452155032</v>
       </c>
       <c r="E185" t="n">
-        <v>0.4168235743944794</v>
+        <v>0.4168235743944761</v>
       </c>
       <c r="F185" t="n">
-        <v>0.7929562849246288</v>
+        <v>0.7929562849246128</v>
       </c>
     </row>
     <row r="186">
@@ -4515,19 +4515,19 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.02526261615080905</v>
+        <v>0.02526261615080927</v>
       </c>
       <c r="C186" t="n">
-        <v>0.3895615535239564</v>
+        <v>0.3895615535239563</v>
       </c>
       <c r="D186" t="n">
-        <v>0.5464454993405825</v>
+        <v>0.5464454993405838</v>
       </c>
       <c r="E186" t="n">
-        <v>0.6261178224554937</v>
+        <v>0.6261178224554916</v>
       </c>
       <c r="F186" t="n">
-        <v>0.7294532737584701</v>
+        <v>0.7294532737584448</v>
       </c>
     </row>
     <row r="187">
@@ -4537,19 +4537,19 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.1612592969824792</v>
+        <v>0.1612592969824795</v>
       </c>
       <c r="C187" t="n">
-        <v>0.4862604511997891</v>
+        <v>0.4862604511997884</v>
       </c>
       <c r="D187" t="n">
-        <v>0.688340873108829</v>
+        <v>0.6883408731088303</v>
       </c>
       <c r="E187" t="n">
-        <v>0.6237924562441366</v>
+        <v>0.6237924562441348</v>
       </c>
       <c r="F187" t="n">
-        <v>0.7559592094424991</v>
+        <v>0.7559592094424783</v>
       </c>
     </row>
     <row r="188">
@@ -4559,19 +4559,19 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.04354170505885184</v>
+        <v>0.0435417050588519</v>
       </c>
       <c r="C188" t="n">
-        <v>0.3131588856089283</v>
+        <v>0.313158885608928</v>
       </c>
       <c r="D188" t="n">
-        <v>0.4298576061169286</v>
+        <v>0.4298576061169294</v>
       </c>
       <c r="E188" t="n">
-        <v>0.5578896354337837</v>
+        <v>0.5578896354337813</v>
       </c>
       <c r="F188" t="n">
-        <v>0.7182813873116668</v>
+        <v>0.7182813873116424</v>
       </c>
     </row>
     <row r="189">
@@ -4584,16 +4584,16 @@
         <v>0.03974537244737159</v>
       </c>
       <c r="C189" t="n">
-        <v>0.2225985030224753</v>
+        <v>0.2225985030224756</v>
       </c>
       <c r="D189" t="n">
-        <v>0.3866029909364883</v>
+        <v>0.3866029909364879</v>
       </c>
       <c r="E189" t="n">
-        <v>0.4579804377980803</v>
+        <v>0.457980437798076</v>
       </c>
       <c r="F189" t="n">
-        <v>0.7513510193537107</v>
+        <v>0.751351019353689</v>
       </c>
     </row>
     <row r="190">
@@ -4603,19 +4603,19 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.04224014813475633</v>
+        <v>0.04224014813475639</v>
       </c>
       <c r="C190" t="n">
-        <v>0.1811791286346302</v>
+        <v>0.1811791286346309</v>
       </c>
       <c r="D190" t="n">
-        <v>0.3189797477094711</v>
+        <v>0.3189797477094707</v>
       </c>
       <c r="E190" t="n">
-        <v>0.4274493583002067</v>
+        <v>0.4274493583002016</v>
       </c>
       <c r="F190" t="n">
-        <v>0.73517725509461</v>
+        <v>0.7351772550945833</v>
       </c>
     </row>
     <row r="191">
@@ -4625,19 +4625,19 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.03348028813264191</v>
+        <v>0.03348028813264197</v>
       </c>
       <c r="C191" t="n">
-        <v>0.1714920508061354</v>
+        <v>0.1714920508061363</v>
       </c>
       <c r="D191" t="n">
-        <v>0.3463472034765034</v>
+        <v>0.3463472034765023</v>
       </c>
       <c r="E191" t="n">
-        <v>0.3617420126511282</v>
+        <v>0.3617420126511229</v>
       </c>
       <c r="F191" t="n">
-        <v>0.7310443678672084</v>
+        <v>0.7310443678671841</v>
       </c>
     </row>
     <row r="192">
@@ -4647,19 +4647,19 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.03134339046064567</v>
+        <v>0.03134339046064562</v>
       </c>
       <c r="C192" t="n">
-        <v>0.1632759253796806</v>
+        <v>0.1632759253796814</v>
       </c>
       <c r="D192" t="n">
-        <v>0.3532567490544187</v>
+        <v>0.3532567490544172</v>
       </c>
       <c r="E192" t="n">
-        <v>0.3926128052833578</v>
+        <v>0.3926128052833521</v>
       </c>
       <c r="F192" t="n">
-        <v>0.7340176575101879</v>
+        <v>0.7340176575101622</v>
       </c>
     </row>
     <row r="193">
@@ -4669,19 +4669,19 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.05077846475261884</v>
+        <v>0.050778464752619</v>
       </c>
       <c r="C193" t="n">
-        <v>0.2944859074886086</v>
+        <v>0.2944859074886082</v>
       </c>
       <c r="D193" t="n">
-        <v>0.5152454224661561</v>
+        <v>0.5152454224661568</v>
       </c>
       <c r="E193" t="n">
-        <v>0.6613119747642863</v>
+        <v>0.6613119747642839</v>
       </c>
       <c r="F193" t="n">
-        <v>0.7430941461917401</v>
+        <v>0.743094146191714</v>
       </c>
     </row>
     <row r="194">
@@ -4691,19 +4691,19 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.06274563811719776</v>
+        <v>0.06274563811719798</v>
       </c>
       <c r="C194" t="n">
-        <v>0.3562010437102737</v>
+        <v>0.3562010437102728</v>
       </c>
       <c r="D194" t="n">
-        <v>0.5044620801962485</v>
+        <v>0.5044620801962506</v>
       </c>
       <c r="E194" t="n">
-        <v>0.7536993504176033</v>
+        <v>0.7536993504176028</v>
       </c>
       <c r="F194" t="n">
-        <v>0.7501069514762957</v>
+        <v>0.7501069514762697</v>
       </c>
     </row>
     <row r="195">
@@ -4713,19 +4713,19 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.1024589606818673</v>
+        <v>0.1024589606818675</v>
       </c>
       <c r="C195" t="n">
-        <v>0.3639562689382803</v>
+        <v>0.3639562689382804</v>
       </c>
       <c r="D195" t="n">
-        <v>0.4183556976362438</v>
+        <v>0.4183556976362446</v>
       </c>
       <c r="E195" t="n">
-        <v>0.5195923445744725</v>
+        <v>0.5195923445744705</v>
       </c>
       <c r="F195" t="n">
-        <v>0.7412837047888289</v>
+        <v>0.741283704788804</v>
       </c>
     </row>
     <row r="196">
@@ -4735,19 +4735,19 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.06546098490104997</v>
+        <v>0.06546098490105014</v>
       </c>
       <c r="C196" t="n">
-        <v>0.3410395709029334</v>
+        <v>0.3410395709029333</v>
       </c>
       <c r="D196" t="n">
-        <v>0.4381715650986466</v>
+        <v>0.4381715650986473</v>
       </c>
       <c r="E196" t="n">
-        <v>0.5569908477276654</v>
+        <v>0.5569908477276635</v>
       </c>
       <c r="F196" t="n">
-        <v>0.768623641765962</v>
+        <v>0.7686236417659446</v>
       </c>
     </row>
     <row r="197">
@@ -4757,19 +4757,19 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.07249575050039521</v>
+        <v>0.07249575050039544</v>
       </c>
       <c r="C197" t="n">
         <v>0.3330718797987473</v>
       </c>
       <c r="D197" t="n">
-        <v>0.4017334521884903</v>
+        <v>0.4017334521884917</v>
       </c>
       <c r="E197" t="n">
-        <v>0.5730028110590044</v>
+        <v>0.5730028110590034</v>
       </c>
       <c r="F197" t="n">
-        <v>0.7589617102110103</v>
+        <v>0.7589617102109888</v>
       </c>
     </row>
     <row r="198">
@@ -4779,19 +4779,19 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.07206081363696108</v>
+        <v>0.0720608136369613</v>
       </c>
       <c r="C198" t="n">
-        <v>0.336617289329707</v>
+        <v>0.3366172893297067</v>
       </c>
       <c r="D198" t="n">
-        <v>0.4504594108717441</v>
+        <v>0.4504594108717455</v>
       </c>
       <c r="E198" t="n">
-        <v>0.6140382811104999</v>
+        <v>0.6140382811104983</v>
       </c>
       <c r="F198" t="n">
-        <v>0.7471029539408924</v>
+        <v>0.7471029539408703</v>
       </c>
     </row>
     <row r="199">
@@ -4801,19 +4801,19 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.1093704328840714</v>
+        <v>0.1093704328840716</v>
       </c>
       <c r="C199" t="n">
-        <v>0.5057312779323105</v>
+        <v>0.5057312779323098</v>
       </c>
       <c r="D199" t="n">
-        <v>0.5857562991489158</v>
+        <v>0.5857562991489176</v>
       </c>
       <c r="E199" t="n">
-        <v>0.7158141888334171</v>
+        <v>0.7158141888334181</v>
       </c>
       <c r="F199" t="n">
-        <v>0.7446274335758698</v>
+        <v>0.7446274335758479</v>
       </c>
     </row>
     <row r="200">
@@ -4823,19 +4823,19 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.07138674585548742</v>
+        <v>0.0713867458554877</v>
       </c>
       <c r="C200" t="n">
-        <v>0.4019891271170625</v>
+        <v>0.4019891271170618</v>
       </c>
       <c r="D200" t="n">
-        <v>0.5940598928254647</v>
+        <v>0.5940598928254667</v>
       </c>
       <c r="E200" t="n">
-        <v>0.7293565515870617</v>
+        <v>0.7293565515870614</v>
       </c>
       <c r="F200" t="n">
-        <v>0.7468196189437307</v>
+        <v>0.7468196189437109</v>
       </c>
     </row>
     <row r="201">
@@ -4845,19 +4845,19 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.08446004412485177</v>
+        <v>0.08446004412485189</v>
       </c>
       <c r="C201" t="n">
-        <v>0.4180401135043795</v>
+        <v>0.4180401135043792</v>
       </c>
       <c r="D201" t="n">
-        <v>0.4894537578961227</v>
+        <v>0.4894537578961234</v>
       </c>
       <c r="E201" t="n">
-        <v>0.5772716352507203</v>
+        <v>0.5772716352507187</v>
       </c>
       <c r="F201" t="n">
-        <v>0.7700944676212487</v>
+        <v>0.7700944676212277</v>
       </c>
     </row>
     <row r="202">
@@ -4867,19 +4867,19 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.07863661220594557</v>
+        <v>0.0786366122059458</v>
       </c>
       <c r="C202" t="n">
-        <v>0.3681509116494957</v>
+        <v>0.3681509116494951</v>
       </c>
       <c r="D202" t="n">
-        <v>0.5255306130636738</v>
+        <v>0.525530613063674</v>
       </c>
       <c r="E202" t="n">
-        <v>0.5943471717281716</v>
+        <v>0.5943471717281688</v>
       </c>
       <c r="F202" t="n">
-        <v>0.785779278180835</v>
+        <v>0.7857792781808121</v>
       </c>
     </row>
     <row r="203">
@@ -4889,19 +4889,19 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.03501759011217656</v>
+        <v>0.03501759011217646</v>
       </c>
       <c r="C203" t="n">
-        <v>0.1565070061419422</v>
+        <v>0.1565070061419431</v>
       </c>
       <c r="D203" t="n">
-        <v>0.3116500507117377</v>
+        <v>0.3116500507117358</v>
       </c>
       <c r="E203" t="n">
-        <v>0.3735713019957915</v>
+        <v>0.3735713019957864</v>
       </c>
       <c r="F203" t="n">
-        <v>0.7076429295027318</v>
+        <v>0.7076429295027074</v>
       </c>
     </row>
     <row r="204">
@@ -4911,19 +4911,19 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.06429113096852522</v>
+        <v>0.06429113096852533</v>
       </c>
       <c r="C204" t="n">
-        <v>0.403187504136447</v>
+        <v>0.4031875041364463</v>
       </c>
       <c r="D204" t="n">
-        <v>0.5105073512938353</v>
+        <v>0.5105073512938366</v>
       </c>
       <c r="E204" t="n">
-        <v>0.686052033251627</v>
+        <v>0.686052033251626</v>
       </c>
       <c r="F204" t="n">
-        <v>0.7404250530709087</v>
+        <v>0.7404250530708876</v>
       </c>
     </row>
     <row r="205">
@@ -4933,19 +4933,19 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.03833251693743508</v>
+        <v>0.03833251693743525</v>
       </c>
       <c r="C205" t="n">
-        <v>0.3696615671994307</v>
+        <v>0.3696615671994304</v>
       </c>
       <c r="D205" t="n">
-        <v>0.4843242750646954</v>
+        <v>0.4843242750646968</v>
       </c>
       <c r="E205" t="n">
-        <v>0.6358759425767956</v>
+        <v>0.6358759425767944</v>
       </c>
       <c r="F205" t="n">
-        <v>0.7252450370363318</v>
+        <v>0.7252450370363068</v>
       </c>
     </row>
     <row r="206">
@@ -4955,19 +4955,19 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.03722119331099642</v>
+        <v>0.03722119331099659</v>
       </c>
       <c r="C206" t="n">
-        <v>0.3332040795695848</v>
+        <v>0.333204079569585</v>
       </c>
       <c r="D206" t="n">
-        <v>0.4279867765393646</v>
+        <v>0.4279867765393656</v>
       </c>
       <c r="E206" t="n">
-        <v>0.5940571084099027</v>
+        <v>0.5940571084099012</v>
       </c>
       <c r="F206" t="n">
-        <v>0.7320991497420197</v>
+        <v>0.7320991497419976</v>
       </c>
     </row>
     <row r="207">
@@ -4977,19 +4977,19 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.03589416712424028</v>
+        <v>0.03589416712424039</v>
       </c>
       <c r="C207" t="n">
-        <v>0.3255502997781578</v>
+        <v>0.3255502997781574</v>
       </c>
       <c r="D207" t="n">
-        <v>0.444790951129782</v>
+        <v>0.4447909511297827</v>
       </c>
       <c r="E207" t="n">
-        <v>0.5923508168046533</v>
+        <v>0.5923508168046515</v>
       </c>
       <c r="F207" t="n">
-        <v>0.7133444455812483</v>
+        <v>0.7133444455812238</v>
       </c>
     </row>
     <row r="208">
@@ -4999,19 +4999,19 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.03706076403596657</v>
+        <v>0.03706076403596658</v>
       </c>
       <c r="C208" t="n">
-        <v>0.2225199627940622</v>
+        <v>0.2225199627940624</v>
       </c>
       <c r="D208" t="n">
-        <v>0.4178591092407399</v>
+        <v>0.4178591092407392</v>
       </c>
       <c r="E208" t="n">
-        <v>0.4888971041171385</v>
+        <v>0.4888971041171342</v>
       </c>
       <c r="F208" t="n">
-        <v>0.7219781037249343</v>
+        <v>0.721978103724908</v>
       </c>
     </row>
     <row r="209">
@@ -5021,19 +5021,19 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.05224766480248805</v>
+        <v>0.05224766480248806</v>
       </c>
       <c r="C209" t="n">
         <v>0.3082933417188517</v>
       </c>
       <c r="D209" t="n">
-        <v>0.452099498870935</v>
+        <v>0.4520994988709344</v>
       </c>
       <c r="E209" t="n">
-        <v>0.5008252783788077</v>
+        <v>0.5008252783788051</v>
       </c>
       <c r="F209" t="n">
-        <v>0.7156205505082914</v>
+        <v>0.7156205505082666</v>
       </c>
     </row>
     <row r="210">
@@ -5043,19 +5043,19 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.05053755303941013</v>
+        <v>0.05053755303941019</v>
       </c>
       <c r="C210" t="n">
-        <v>0.3508170701142912</v>
+        <v>0.350817070114291</v>
       </c>
       <c r="D210" t="n">
-        <v>0.4465786591270015</v>
+        <v>0.4465786591270014</v>
       </c>
       <c r="E210" t="n">
-        <v>0.5320506520687589</v>
+        <v>0.532050652068757</v>
       </c>
       <c r="F210" t="n">
-        <v>0.716184233194622</v>
+        <v>0.7161842331945992</v>
       </c>
     </row>
     <row r="211">
@@ -5065,19 +5065,19 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.07184609643913398</v>
+        <v>0.0718460964391341</v>
       </c>
       <c r="C211" t="n">
-        <v>0.4556378144086807</v>
+        <v>0.4556378144086803</v>
       </c>
       <c r="D211" t="n">
-        <v>0.5706272535762167</v>
+        <v>0.5706272535762178</v>
       </c>
       <c r="E211" t="n">
-        <v>0.6619083500515544</v>
+        <v>0.6619083500515542</v>
       </c>
       <c r="F211" t="n">
-        <v>0.7419518888516899</v>
+        <v>0.7419518888516686</v>
       </c>
     </row>
     <row r="212">
@@ -5087,19 +5087,19 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.02753613639077699</v>
+        <v>0.0275361363907771</v>
       </c>
       <c r="C212" t="n">
-        <v>0.3550268894094964</v>
+        <v>0.3550268894094966</v>
       </c>
       <c r="D212" t="n">
-        <v>0.4638401337583393</v>
+        <v>0.4638401337583395</v>
       </c>
       <c r="E212" t="n">
-        <v>0.541206676752896</v>
+        <v>0.5412066767528931</v>
       </c>
       <c r="F212" t="n">
-        <v>0.7399091508126221</v>
+        <v>0.7399091508125967</v>
       </c>
     </row>
     <row r="213">
@@ -5109,19 +5109,19 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.02743970622587116</v>
+        <v>0.02743970622587128</v>
       </c>
       <c r="C213" t="n">
-        <v>0.3157287750050366</v>
+        <v>0.3157287750050368</v>
       </c>
       <c r="D213" t="n">
-        <v>0.3884674133761822</v>
+        <v>0.3884674133761827</v>
       </c>
       <c r="E213" t="n">
-        <v>0.5160439935976093</v>
+        <v>0.5160439935976072</v>
       </c>
       <c r="F213" t="n">
-        <v>0.7571744946240508</v>
+        <v>0.7571744946240281</v>
       </c>
     </row>
     <row r="214">
@@ -5131,19 +5131,19 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.08479523421276663</v>
+        <v>0.0847952342127668</v>
       </c>
       <c r="C214" t="n">
-        <v>0.4338071959609641</v>
+        <v>0.4338071959609636</v>
       </c>
       <c r="D214" t="n">
-        <v>0.5594947600411166</v>
+        <v>0.559494760041118</v>
       </c>
       <c r="E214" t="n">
-        <v>0.6659349833507207</v>
+        <v>0.6659349833507198</v>
       </c>
       <c r="F214" t="n">
-        <v>0.75347311153167</v>
+        <v>0.7534731115316493</v>
       </c>
     </row>
     <row r="215">
@@ -5153,19 +5153,19 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.05111601036937787</v>
+        <v>0.05111601036937788</v>
       </c>
       <c r="C215" t="n">
-        <v>0.2460600954523327</v>
+        <v>0.2460600954523326</v>
       </c>
       <c r="D215" t="n">
-        <v>0.3408272104395775</v>
+        <v>0.3408272104395773</v>
       </c>
       <c r="E215" t="n">
-        <v>0.5276880673759273</v>
+        <v>0.527688067375925</v>
       </c>
       <c r="F215" t="n">
-        <v>0.7165639083210802</v>
+        <v>0.7165639083210565</v>
       </c>
     </row>
     <row r="216">
@@ -5175,19 +5175,19 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.05976616657025133</v>
+        <v>0.05976616657025145</v>
       </c>
       <c r="C216" t="n">
-        <v>0.2905309147304898</v>
+        <v>0.2905309147304899</v>
       </c>
       <c r="D216" t="n">
-        <v>0.4128408425857</v>
+        <v>0.4128408425857006</v>
       </c>
       <c r="E216" t="n">
-        <v>0.5534090841555227</v>
+        <v>0.5534090841555196</v>
       </c>
       <c r="F216" t="n">
-        <v>0.7557383663381724</v>
+        <v>0.7557383663381488</v>
       </c>
     </row>
     <row r="217">
@@ -5197,19 +5197,19 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.1033064947733488</v>
+        <v>0.1033064947733492</v>
       </c>
       <c r="C217" t="n">
-        <v>0.6496257656132259</v>
+        <v>0.6496257656132253</v>
       </c>
       <c r="D217" t="n">
-        <v>0.827377508282701</v>
+        <v>0.8273775082827005</v>
       </c>
       <c r="E217" t="n">
-        <v>0.5431791241876301</v>
+        <v>0.5431791241876263</v>
       </c>
       <c r="F217" t="n">
-        <v>0.7822953477959576</v>
+        <v>0.7822953477959296</v>
       </c>
     </row>
     <row r="218">
@@ -5219,19 +5219,19 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.1185737165699622</v>
+        <v>0.1185737165699624</v>
       </c>
       <c r="C218" t="n">
-        <v>0.6358829621870316</v>
+        <v>0.6358829621870302</v>
       </c>
       <c r="D218" t="n">
-        <v>0.7270826925744658</v>
+        <v>0.7270826925744677</v>
       </c>
       <c r="E218" t="n">
-        <v>0.8176550809089022</v>
+        <v>0.8176550809089036</v>
       </c>
       <c r="F218" t="n">
-        <v>0.7434745049738261</v>
+        <v>0.7434745049738056</v>
       </c>
     </row>
     <row r="219">
@@ -5241,19 +5241,19 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.2979647173466677</v>
+        <v>0.2979647173466679</v>
       </c>
       <c r="C219" t="n">
-        <v>0.8889043690118127</v>
+        <v>0.888904369011813</v>
       </c>
       <c r="D219" t="n">
-        <v>0.7957318794335831</v>
+        <v>0.7957318794335826</v>
       </c>
       <c r="E219" t="n">
-        <v>0.4433526375833076</v>
+        <v>0.443352637583303</v>
       </c>
       <c r="F219" t="n">
-        <v>0.6583271799920005</v>
+        <v>0.6583271799919691</v>
       </c>
     </row>
     <row r="220">
@@ -5263,19 +5263,19 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.08550473982058548</v>
+        <v>0.08550473982058576</v>
       </c>
       <c r="C220" t="n">
-        <v>0.5788625728405385</v>
+        <v>0.578862572840538</v>
       </c>
       <c r="D220" t="n">
-        <v>0.7618548508924239</v>
+        <v>0.7618548508924246</v>
       </c>
       <c r="E220" t="n">
-        <v>0.6384719885261456</v>
+        <v>0.6384719885261423</v>
       </c>
       <c r="F220" t="n">
-        <v>0.7630266515618382</v>
+        <v>0.7630266515618094</v>
       </c>
     </row>
     <row r="221">
@@ -5285,19 +5285,19 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.1362664166062623</v>
+        <v>0.1362664166062627</v>
       </c>
       <c r="C221" t="n">
-        <v>0.6653298055889085</v>
+        <v>0.665329805588907</v>
       </c>
       <c r="D221" t="n">
-        <v>0.7292123029644918</v>
+        <v>0.7292123029644941</v>
       </c>
       <c r="E221" t="n">
-        <v>0.8476851414630918</v>
+        <v>0.8476851414630945</v>
       </c>
       <c r="F221" t="n">
-        <v>0.7368573806219674</v>
+        <v>0.7368573806219472</v>
       </c>
     </row>
     <row r="222">
@@ -5307,19 +5307,19 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.05889422554764656</v>
+        <v>0.05889422554764663</v>
       </c>
       <c r="C222" t="n">
-        <v>0.388640346205906</v>
+        <v>0.3886403462059062</v>
       </c>
       <c r="D222" t="n">
-        <v>0.4713218615400863</v>
+        <v>0.4713218615400862</v>
       </c>
       <c r="E222" t="n">
-        <v>0.5126351742479789</v>
+        <v>0.5126351742479756</v>
       </c>
       <c r="F222" t="n">
-        <v>0.7685963900628796</v>
+        <v>0.7685963900628563</v>
       </c>
     </row>
     <row r="223">
@@ -5329,19 +5329,19 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.1627150076412407</v>
+        <v>0.1627150076412409</v>
       </c>
       <c r="C223" t="n">
         <v>1</v>
       </c>
       <c r="D223" t="n">
-        <v>0.7931948412349721</v>
+        <v>0.793194841234972</v>
       </c>
       <c r="E223" t="n">
-        <v>0.5149236178984772</v>
+        <v>0.5149236178984722</v>
       </c>
       <c r="F223" t="n">
-        <v>0.66822369350904</v>
+        <v>0.6682236935090052</v>
       </c>
     </row>
     <row r="224">
@@ -5351,19 +5351,19 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.07352222498457608</v>
+        <v>0.07352222498457625</v>
       </c>
       <c r="C224" t="n">
-        <v>0.5021213815869879</v>
+        <v>0.5021213815869855</v>
       </c>
       <c r="D224" t="n">
-        <v>0.6730936455023943</v>
+        <v>0.6730936455023959</v>
       </c>
       <c r="E224" t="n">
-        <v>0.927315678894427</v>
+        <v>0.92731567889443</v>
       </c>
       <c r="F224" t="n">
-        <v>0.6789249359299109</v>
+        <v>0.6789249359298885</v>
       </c>
     </row>
     <row r="225">
@@ -5373,19 +5373,19 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.1107104100974744</v>
+        <v>0.1107104100974747</v>
       </c>
       <c r="C225" t="n">
-        <v>0.5968972356364537</v>
+        <v>0.5968972356364519</v>
       </c>
       <c r="D225" t="n">
-        <v>0.7201463941783446</v>
+        <v>0.7201463941783471</v>
       </c>
       <c r="E225" t="n">
-        <v>0.8278976160884476</v>
+        <v>0.8278976160884493</v>
       </c>
       <c r="F225" t="n">
-        <v>0.7335879833614677</v>
+        <v>0.733587983361446</v>
       </c>
     </row>
     <row r="226">
@@ -5395,19 +5395,19 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.09972857379206182</v>
+        <v>0.09972857379206196</v>
       </c>
       <c r="C226" t="n">
-        <v>0.5096222852492758</v>
+        <v>0.5096222852492754</v>
       </c>
       <c r="D226" t="n">
         <v>0.5577223744817261</v>
       </c>
       <c r="E226" t="n">
-        <v>0.5668283425620322</v>
+        <v>0.5668283425620311</v>
       </c>
       <c r="F226" t="n">
-        <v>0.7525365401266751</v>
+        <v>0.7525365401266544</v>
       </c>
     </row>
     <row r="227">
@@ -5417,19 +5417,19 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.06379190028166724</v>
+        <v>0.06379190028166735</v>
       </c>
       <c r="C227" t="n">
-        <v>0.3927482744142894</v>
+        <v>0.3927482744142891</v>
       </c>
       <c r="D227" t="n">
-        <v>0.524041919821472</v>
+        <v>0.5240419198214719</v>
       </c>
       <c r="E227" t="n">
-        <v>0.5663305954433561</v>
+        <v>0.5663305954433532</v>
       </c>
       <c r="F227" t="n">
-        <v>0.7542793850500989</v>
+        <v>0.7542793850500772</v>
       </c>
     </row>
     <row r="228">
@@ -5442,16 +5442,16 @@
         <v>0.1396242568101373</v>
       </c>
       <c r="C228" t="n">
-        <v>0.6206723151522767</v>
+        <v>0.6206723151522772</v>
       </c>
       <c r="D228" t="n">
-        <v>0.3836985529842901</v>
+        <v>0.3836985529842879</v>
       </c>
       <c r="E228" t="n">
-        <v>0.3390783348860865</v>
+        <v>0.3390783348860832</v>
       </c>
       <c r="F228" t="n">
-        <v>0.7889238430131256</v>
+        <v>0.7889238430131008</v>
       </c>
     </row>
     <row r="229">
@@ -5461,19 +5461,19 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.1470064225611687</v>
+        <v>0.147006422561169</v>
       </c>
       <c r="C229" t="n">
-        <v>0.843992457516</v>
+        <v>0.8439924575159986</v>
       </c>
       <c r="D229" t="n">
-        <v>0.7817858106399588</v>
+        <v>0.7817858106399607</v>
       </c>
       <c r="E229" t="n">
-        <v>0.7182779883356047</v>
+        <v>0.7182779883356046</v>
       </c>
       <c r="F229" t="n">
-        <v>0.735390443313108</v>
+        <v>0.7353904433130819</v>
       </c>
     </row>
     <row r="230">
@@ -5483,19 +5483,19 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.06660760531344398</v>
+        <v>0.06660760531344399</v>
       </c>
       <c r="C230" t="n">
-        <v>0.441668741774669</v>
+        <v>0.4416687417746689</v>
       </c>
       <c r="D230" t="n">
-        <v>0.4557820006372764</v>
+        <v>0.455782000637276</v>
       </c>
       <c r="E230" t="n">
-        <v>0.5274407807244366</v>
+        <v>0.5274407807244339</v>
       </c>
       <c r="F230" t="n">
-        <v>0.7318165231887509</v>
+        <v>0.7318165231887244</v>
       </c>
     </row>
     <row r="231">
@@ -5505,19 +5505,19 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.1450018932578629</v>
+        <v>0.1450018932578631</v>
       </c>
       <c r="C231" t="n">
-        <v>0.5806177232638003</v>
+        <v>0.5806177232638</v>
       </c>
       <c r="D231" t="n">
-        <v>0.4796602502743955</v>
+        <v>0.4796602502743966</v>
       </c>
       <c r="E231" t="n">
-        <v>0.5868301372604697</v>
+        <v>0.5868301372604714</v>
       </c>
       <c r="F231" t="n">
-        <v>0.8479784332797008</v>
+        <v>0.8479784332796989</v>
       </c>
     </row>
     <row r="232">
@@ -5527,19 +5527,19 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.1299425948163339</v>
+        <v>0.1299425948163342</v>
       </c>
       <c r="C232" t="n">
-        <v>0.5420475226589927</v>
+        <v>0.5420475226589921</v>
       </c>
       <c r="D232" t="n">
-        <v>0.5028611736642677</v>
+        <v>0.5028611736642691</v>
       </c>
       <c r="E232" t="n">
-        <v>0.5981427511143236</v>
+        <v>0.5981427511143244</v>
       </c>
       <c r="F232" t="n">
-        <v>0.8137240415100608</v>
+        <v>0.8137240415100503</v>
       </c>
     </row>
     <row r="233">
@@ -5549,19 +5549,19 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.09826485992131082</v>
+        <v>0.09826485992131105</v>
       </c>
       <c r="C233" t="n">
-        <v>0.4855273191409102</v>
+        <v>0.4855273191409097</v>
       </c>
       <c r="D233" t="n">
-        <v>0.6592829017107147</v>
+        <v>0.6592829017107155</v>
       </c>
       <c r="E233" t="n">
-        <v>0.6423602262051605</v>
+        <v>0.6423602262051596</v>
       </c>
       <c r="F233" t="n">
-        <v>0.8006866748469876</v>
+        <v>0.8006866748469734</v>
       </c>
     </row>
     <row r="234">
@@ -5571,19 +5571,19 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.1447816360330592</v>
+        <v>0.1447816360330594</v>
       </c>
       <c r="C234" t="n">
         <v>0.5962540385409167</v>
       </c>
       <c r="D234" t="n">
-        <v>0.4974485700120665</v>
+        <v>0.4974485700120676</v>
       </c>
       <c r="E234" t="n">
-        <v>0.5512194908795292</v>
+        <v>0.55121949087953</v>
       </c>
       <c r="F234" t="n">
-        <v>0.8561383230166836</v>
+        <v>0.8561383230166826</v>
       </c>
     </row>
   </sheetData>
